--- a/Tables (1).xlsx
+++ b/Tables (1).xlsx
@@ -19869,9 +19869,6 @@
       <c r="C2" t="str">
         <v>CGM</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
       <c r="E2" t="str">
         <v>Shri Veera Nageswara Rao Kothapalli</v>
       </c>
@@ -19883,9 +19880,6 @@
       </c>
       <c r="H2" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I2" t="str">
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -19898,9 +19892,6 @@
       <c r="C3" t="str">
         <v>GM(EB)</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
       <c r="E3" t="str">
         <v>G KUMARESHAN</v>
       </c>
@@ -19912,9 +19903,6 @@
       </c>
       <c r="H3" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -19927,9 +19915,6 @@
       <c r="C4" t="str">
         <v>DGM(EB)</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
       <c r="E4" t="str">
         <v>VENKATA CHALAPATHI PEMMARAJU</v>
       </c>
@@ -19941,9 +19926,6 @@
       </c>
       <c r="H4" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -19956,9 +19938,6 @@
       <c r="C5" t="str">
         <v>AGM</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
       <c r="E5" t="str">
         <v>Jithendran</v>
       </c>
@@ -19970,9 +19949,6 @@
       </c>
       <c r="H5" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -19985,9 +19961,6 @@
       <c r="C6" t="str">
         <v>SDE(EB)</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
       <c r="E6" t="str">
         <v>M Bhaskar</v>
       </c>
@@ -19999,9 +19972,6 @@
       </c>
       <c r="H6" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -20014,9 +19984,6 @@
       <c r="C7" t="str">
         <v>SDE(EB)</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
       <c r="E7" t="str">
         <v>Ranjit Halder</v>
       </c>
@@ -20028,9 +19995,6 @@
       </c>
       <c r="H7" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -20043,9 +20007,6 @@
       <c r="C8" t="str">
         <v>CGM</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
       <c r="E8" t="str">
         <v>SESHACHALAM M</v>
       </c>
@@ -20057,9 +20018,6 @@
       </c>
       <c r="H8" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -20072,9 +20030,6 @@
       <c r="C9" t="str">
         <v>GM (EB)</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
       <c r="E9" t="str">
         <v>TATA VENKATA PRASAD</v>
       </c>
@@ -20086,9 +20041,6 @@
       </c>
       <c r="H9" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -20101,9 +20053,6 @@
       <c r="C10" t="str">
         <v>DGM (EB)</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
       <c r="E10" t="str">
         <v>S MALLIKARJUNA RAO</v>
       </c>
@@ -20115,9 +20064,6 @@
       </c>
       <c r="H10" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -20130,9 +20076,6 @@
       <c r="C11" t="str">
         <v>AGM (EB)</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
       <c r="E11" t="str">
         <v>V Hemanth Prasad</v>
       </c>
@@ -20144,9 +20087,6 @@
       </c>
       <c r="H11" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -20159,9 +20099,6 @@
       <c r="C12" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
       <c r="E12" t="str">
         <v>V Pitchireddy Penugonda</v>
       </c>
@@ -20173,9 +20110,6 @@
       </c>
       <c r="H12" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -20188,9 +20122,6 @@
       <c r="C13" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
       <c r="E13" t="str">
         <v>R Venu Gopal</v>
       </c>
@@ -20202,9 +20133,6 @@
       </c>
       <c r="H13" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -20217,9 +20145,6 @@
       <c r="C14" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
       <c r="E14" t="str">
         <v>Ravi Kumar Bonigala</v>
       </c>
@@ -20231,9 +20156,6 @@
       </c>
       <c r="H14" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -20246,9 +20168,6 @@
       <c r="C15" t="str">
         <v>SDE</v>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
       <c r="E15" t="str">
         <v>G.Venkateswara Rao</v>
       </c>
@@ -20260,9 +20179,6 @@
       </c>
       <c r="H15" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -20275,9 +20191,6 @@
       <c r="C16" t="str">
         <v>CGM</v>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
       <c r="E16" t="str">
         <v>Ashok Kr Jha</v>
       </c>
@@ -20289,9 +20202,6 @@
       </c>
       <c r="H16" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -20304,9 +20214,6 @@
       <c r="C17" t="str">
         <v>GM</v>
       </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
       <c r="E17" t="str">
         <v>S VARA PRASAD KALA</v>
       </c>
@@ -20318,9 +20225,6 @@
       </c>
       <c r="H17" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -20333,9 +20237,6 @@
       <c r="C18" t="str">
         <v>AGM(EB)-LC</v>
       </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
       <c r="E18" t="str">
         <v>Madan Singh</v>
       </c>
@@ -20347,9 +20248,6 @@
       </c>
       <c r="H18" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I18" t="str">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -20362,9 +20260,6 @@
       <c r="C19" t="str">
         <v>SDE(EB-LC)</v>
       </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
       <c r="E19" t="str">
         <v>KALIKIRI BALAJI</v>
       </c>
@@ -20376,9 +20271,6 @@
       </c>
       <c r="H19" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I19" t="str">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -20391,9 +20283,6 @@
       <c r="C20" t="str">
         <v>SDE(EB-LC)</v>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
       <c r="E20" t="str">
         <v>SRINIVASA RAO GUDE</v>
       </c>
@@ -20405,9 +20294,6 @@
       </c>
       <c r="H20" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I20" t="str">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -20420,9 +20306,6 @@
       <c r="C21" t="str">
         <v>AGM(EB)-SALES</v>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
       <c r="E21" t="str">
         <v>Ravi shankar Chaganti</v>
       </c>
@@ -20434,9 +20317,6 @@
       </c>
       <c r="H21" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -20449,9 +20329,6 @@
       <c r="C22" t="str">
         <v>SDE(EB-SALES)</v>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
       <c r="E22" t="str">
         <v>SATYAJOTHINATH</v>
       </c>
@@ -20463,9 +20340,6 @@
       </c>
       <c r="H22" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I22" t="str">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -20478,9 +20352,6 @@
       <c r="C23" t="str">
         <v>CGM</v>
       </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
       <c r="E23" t="str">
         <v>Ravindra Kumar Choudhary</v>
       </c>
@@ -20492,9 +20363,6 @@
       </c>
       <c r="H23" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I23" t="str">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -20507,9 +20375,6 @@
       <c r="C24" t="str">
         <v>GM</v>
       </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
       <c r="E24" t="str">
         <v>Animesh Kumar</v>
       </c>
@@ -20521,9 +20386,6 @@
       </c>
       <c r="H24" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I24" t="str">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -20536,9 +20398,6 @@
       <c r="C25" t="str">
         <v>DGM</v>
       </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
       <c r="E25" t="str">
         <v>K K AMBASTHA</v>
       </c>
@@ -20550,9 +20409,6 @@
       </c>
       <c r="H25" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I25" t="str">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -20565,9 +20421,6 @@
       <c r="C26" t="str">
         <v>AGM LC</v>
       </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
       <c r="E26" t="str">
         <v>Raju Kumar</v>
       </c>
@@ -20579,9 +20432,6 @@
       </c>
       <c r="H26" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -20594,9 +20444,6 @@
       <c r="C27" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
       <c r="E27" t="str">
         <v>U.C. Choudhary</v>
       </c>
@@ -20608,9 +20455,6 @@
       </c>
       <c r="H27" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I27" t="str">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -20623,9 +20467,6 @@
       <c r="C28" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
       <c r="E28" t="str">
         <v>Mukesh Kumar Modi</v>
       </c>
@@ -20637,9 +20478,6 @@
       </c>
       <c r="H28" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I28" t="str">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -20652,9 +20490,6 @@
       <c r="C29" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
       <c r="E29" t="str">
         <v>MANI PRABHA</v>
       </c>
@@ -20666,9 +20501,6 @@
       </c>
       <c r="H29" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I29" t="str">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -20681,9 +20513,6 @@
       <c r="C30" t="str">
         <v>JTO LC</v>
       </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
       <c r="E30" t="str">
         <v>Shatrugna Kumar Gupta</v>
       </c>
@@ -20695,9 +20524,6 @@
       </c>
       <c r="H30" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I30" t="str">
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -20710,9 +20536,6 @@
       <c r="C31" t="str">
         <v>JTO LC</v>
       </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
       <c r="E31" t="str">
         <v>Lankesh Kr Jha</v>
       </c>
@@ -20724,9 +20547,6 @@
       </c>
       <c r="H31" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I31" t="str">
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -20739,9 +20559,6 @@
       <c r="C32" t="str">
         <v>CGM</v>
       </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
       <c r="E32" t="str">
         <v>Vijay Kumar Chhablani</v>
       </c>
@@ -20753,9 +20570,6 @@
       </c>
       <c r="H32" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I32" t="str">
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -20768,9 +20582,6 @@
       <c r="C33" t="str">
         <v>GM</v>
       </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
       <c r="E33" t="str">
         <v>Bhoomika Gupta</v>
       </c>
@@ -20782,9 +20593,6 @@
       </c>
       <c r="H33" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I33" t="str">
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -20797,9 +20605,6 @@
       <c r="C34" t="str">
         <v>DGM</v>
       </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
       <c r="E34" t="str">
         <v>V M Singh</v>
       </c>
@@ -20811,9 +20616,6 @@
       </c>
       <c r="H34" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I34" t="str">
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -20826,9 +20628,6 @@
       <c r="C35" t="str">
         <v>SDE LC/CRM</v>
       </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
       <c r="E35" t="str">
         <v>MUKESH KUMAR KAUSHIK</v>
       </c>
@@ -20840,9 +20639,6 @@
       </c>
       <c r="H35" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I35" t="str">
-        <v/>
       </c>
     </row>
     <row r="36">
@@ -20855,9 +20651,6 @@
       <c r="C36" t="str">
         <v>SDE EB-SA</v>
       </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
       <c r="E36" t="str">
         <v>Chandrajeet Yadav</v>
       </c>
@@ -20869,9 +20662,6 @@
       </c>
       <c r="H36" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I36" t="str">
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -20884,9 +20674,6 @@
       <c r="C37" t="str">
         <v>CGM</v>
       </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
       <c r="E37" t="str">
         <v>PARTHIBAN S</v>
       </c>
@@ -20898,9 +20685,6 @@
       </c>
       <c r="H37" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I37" t="str">
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -20913,9 +20697,6 @@
       <c r="C38" t="str">
         <v>GM</v>
       </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
       <c r="E38" t="str">
         <v>RAJIV KUMAR</v>
       </c>
@@ -20927,9 +20708,6 @@
       </c>
       <c r="H38" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I38" t="str">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -20942,9 +20720,6 @@
       <c r="C39" t="str">
         <v>DGM EB SDSA</v>
       </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
       <c r="E39" t="str">
         <v>USHA KUMARI S</v>
       </c>
@@ -20956,9 +20731,6 @@
       </c>
       <c r="H39" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I39" t="str">
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -20971,9 +20743,6 @@
       <c r="C40" t="str">
         <v>DGM EB SALES</v>
       </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
       <c r="E40" t="str">
         <v>RAGHURAMAN G</v>
       </c>
@@ -20985,9 +20754,6 @@
       </c>
       <c r="H40" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I40" t="str">
-        <v/>
       </c>
     </row>
     <row r="41">
@@ -21000,9 +20766,6 @@
       <c r="C41" t="str">
         <v>AGM SDSA</v>
       </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
       <c r="E41" t="str">
         <v>ELIZABETH JULIE</v>
       </c>
@@ -21014,9 +20777,6 @@
       </c>
       <c r="H41" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I41" t="str">
-        <v/>
       </c>
     </row>
     <row r="42">
@@ -21029,9 +20789,6 @@
       <c r="C42" t="str">
         <v>SDE SDSA3</v>
       </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
       <c r="E42" t="str">
         <v>PREETHI J</v>
       </c>
@@ -21043,9 +20800,6 @@
       </c>
       <c r="H42" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I42" t="str">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -21058,9 +20812,6 @@
       <c r="C43" t="str">
         <v>SDE SDSA4</v>
       </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
       <c r="E43" t="str">
         <v>ROOBAJA E</v>
       </c>
@@ -21072,9 +20823,6 @@
       </c>
       <c r="H43" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I43" t="str">
-        <v/>
       </c>
     </row>
     <row r="44">
@@ -21087,9 +20835,6 @@
       <c r="C44" t="str">
         <v>SDE SDSA1</v>
       </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
       <c r="E44" t="str">
         <v>SANJOO SINGH</v>
       </c>
@@ -21101,9 +20846,6 @@
       </c>
       <c r="H44" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I44" t="str">
-        <v/>
       </c>
     </row>
     <row r="45">
@@ -21116,9 +20858,6 @@
       <c r="C45" t="str">
         <v>JTO SDSA2</v>
       </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
       <c r="E45" t="str">
         <v>V SHYAMALA DEVI</v>
       </c>
@@ -21130,9 +20869,6 @@
       </c>
       <c r="H45" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I45" t="str">
-        <v/>
       </c>
     </row>
     <row r="46">
@@ -21145,9 +20881,6 @@
       <c r="C46" t="str">
         <v>GM LC</v>
       </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
       <c r="E46" t="str">
         <v>Upendra Tiwari</v>
       </c>
@@ -21159,9 +20892,6 @@
       </c>
       <c r="H46" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I46" t="str">
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -21174,9 +20904,6 @@
       <c r="C47" t="str">
         <v>DGM LC</v>
       </c>
-      <c r="D47" t="str">
-        <v/>
-      </c>
       <c r="E47" t="str">
         <v>Ramawtar Meena</v>
       </c>
@@ -21188,9 +20915,6 @@
       </c>
       <c r="H47" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I47" t="str">
-        <v/>
       </c>
     </row>
     <row r="48">
@@ -21203,9 +20927,6 @@
       <c r="C48" t="str">
         <v>AGM LC</v>
       </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
       <c r="E48" t="str">
         <v>Vijay Singh</v>
       </c>
@@ -21217,9 +20938,6 @@
       </c>
       <c r="H48" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I48" t="str">
-        <v/>
       </c>
     </row>
     <row r="49">
@@ -21232,9 +20950,6 @@
       <c r="C49" t="str">
         <v>DM LC</v>
       </c>
-      <c r="D49" t="str">
-        <v/>
-      </c>
       <c r="E49" t="str">
         <v>Satya Sasidhar M</v>
       </c>
@@ -21246,9 +20961,6 @@
       </c>
       <c r="H49" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I49" t="str">
-        <v/>
       </c>
     </row>
     <row r="50">
@@ -21261,9 +20973,6 @@
       <c r="C50" t="str">
         <v>DM LC</v>
       </c>
-      <c r="D50" t="str">
-        <v/>
-      </c>
       <c r="E50" t="str">
         <v>Mallesham Kasaveni</v>
       </c>
@@ -21275,9 +20984,6 @@
       </c>
       <c r="H50" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I50" t="str">
-        <v/>
       </c>
     </row>
     <row r="51">
@@ -21290,9 +20996,6 @@
       <c r="C51" t="str">
         <v>DM LC</v>
       </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
       <c r="E51" t="str">
         <v>Vemula Rajeshwar</v>
       </c>
@@ -21304,9 +21007,6 @@
       </c>
       <c r="H51" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I51" t="str">
-        <v/>
       </c>
     </row>
     <row r="52">
@@ -21319,9 +21019,6 @@
       <c r="C52" t="str">
         <v>AM LC</v>
       </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
       <c r="E52" t="str">
         <v>Alok Ranjan</v>
       </c>
@@ -21333,9 +21030,6 @@
       </c>
       <c r="H52" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I52" t="str">
-        <v/>
       </c>
     </row>
     <row r="53">
@@ -21348,9 +21042,6 @@
       <c r="C53" t="str">
         <v>CGM</v>
       </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
       <c r="E53" t="str">
         <v>Shri G Kevlani</v>
       </c>
@@ -21362,9 +21053,6 @@
       </c>
       <c r="H53" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I53" t="str">
-        <v/>
       </c>
     </row>
     <row r="54">
@@ -21377,9 +21065,6 @@
       <c r="C54" t="str">
         <v>PGM EB</v>
       </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
       <c r="E54" t="str">
         <v>Shri Manoj Kumar</v>
       </c>
@@ -21391,9 +21076,6 @@
       </c>
       <c r="H54" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I54" t="str">
-        <v/>
       </c>
     </row>
     <row r="55">
@@ -21406,9 +21088,6 @@
       <c r="C55" t="str">
         <v>DGM LC &amp; GoG</v>
       </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
       <c r="E55" t="str">
         <v>Shri AJAY HASWANI</v>
       </c>
@@ -21420,9 +21099,6 @@
       </c>
       <c r="H55" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I55" t="str">
-        <v/>
       </c>
     </row>
     <row r="56">
@@ -21435,9 +21111,6 @@
       <c r="C56" t="str">
         <v>AGM LC_SA</v>
       </c>
-      <c r="D56" t="str">
-        <v/>
-      </c>
       <c r="E56" t="str">
         <v>Shri Vikas Deolikar</v>
       </c>
@@ -21449,9 +21122,6 @@
       </c>
       <c r="H56" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I56" t="str">
-        <v/>
       </c>
     </row>
     <row r="57">
@@ -21464,9 +21134,6 @@
       <c r="C57" t="str">
         <v>AGM CRM_SD</v>
       </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
       <c r="E57" t="str">
         <v>Ms. Padminee Kochak</v>
       </c>
@@ -21478,9 +21145,6 @@
       </c>
       <c r="H57" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I57" t="str">
-        <v/>
       </c>
     </row>
     <row r="58">
@@ -21493,9 +21157,6 @@
       <c r="C58" t="str">
         <v>SDE LC_SA</v>
       </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
       <c r="E58" t="str">
         <v>Ms. Aarti Chungade</v>
       </c>
@@ -21507,9 +21168,6 @@
       </c>
       <c r="H58" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I58" t="str">
-        <v/>
       </c>
     </row>
     <row r="59">
@@ -21522,9 +21180,6 @@
       <c r="C59" t="str">
         <v>JTO LC_SA</v>
       </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
       <c r="E59" t="str">
         <v>Shri N D Kadiya</v>
       </c>
@@ -21536,9 +21191,6 @@
       </c>
       <c r="H59" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I59" t="str">
-        <v/>
       </c>
     </row>
     <row r="60">
@@ -21551,9 +21203,6 @@
       <c r="C60" t="str">
         <v>JTO LC_SD</v>
       </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
       <c r="E60" t="str">
         <v>Shri Pankaj Juneja</v>
       </c>
@@ -21565,9 +21214,6 @@
       </c>
       <c r="H60" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I60" t="str">
-        <v/>
       </c>
     </row>
     <row r="61">
@@ -21580,9 +21226,6 @@
       <c r="C61" t="str">
         <v>CGM</v>
       </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
       <c r="E61" t="str">
         <v>Sh. ANIL KUMAR GUPTA</v>
       </c>
@@ -21594,9 +21237,6 @@
       </c>
       <c r="H61" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I61" t="str">
-        <v/>
       </c>
     </row>
     <row r="62">
@@ -21609,9 +21249,6 @@
       <c r="C62" t="str">
         <v>GM</v>
       </c>
-      <c r="D62" t="str">
-        <v/>
-      </c>
       <c r="E62" t="str">
         <v>Sh. Rajan Kamboj</v>
       </c>
@@ -21623,9 +21260,6 @@
       </c>
       <c r="H62" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I62" t="str">
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -21638,9 +21272,6 @@
       <c r="C63" t="str">
         <v>DGM</v>
       </c>
-      <c r="D63" t="str">
-        <v/>
-      </c>
       <c r="E63" t="str">
         <v>Sh. Deepak Kumar Gupta</v>
       </c>
@@ -21652,9 +21283,6 @@
       </c>
       <c r="H63" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I63" t="str">
-        <v/>
       </c>
     </row>
     <row r="64">
@@ -21667,9 +21295,6 @@
       <c r="C64" t="str">
         <v>AGM</v>
       </c>
-      <c r="D64" t="str">
-        <v/>
-      </c>
       <c r="E64" t="str">
         <v>Ritesh Bahl</v>
       </c>
@@ -21681,9 +21306,6 @@
       </c>
       <c r="H64" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I64" t="str">
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -21696,9 +21318,6 @@
       <c r="C65" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D65" t="str">
-        <v/>
-      </c>
       <c r="E65" t="str">
         <v>Deepak Kumar Gupta</v>
       </c>
@@ -21710,9 +21329,6 @@
       </c>
       <c r="H65" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I65" t="str">
-        <v/>
       </c>
     </row>
     <row r="66">
@@ -21725,9 +21341,6 @@
       <c r="C66" t="str">
         <v>SDE EB</v>
       </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
       <c r="E66" t="str">
         <v>Sunil Kumar</v>
       </c>
@@ -21739,9 +21352,6 @@
       </c>
       <c r="H66" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I66" t="str">
-        <v/>
       </c>
     </row>
     <row r="67">
@@ -21754,9 +21364,6 @@
       <c r="C67" t="str">
         <v>CGM</v>
       </c>
-      <c r="D67" t="str">
-        <v/>
-      </c>
       <c r="E67" t="str">
         <v>Amit singal</v>
       </c>
@@ -21768,9 +21375,6 @@
       </c>
       <c r="H67" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I67" t="str">
-        <v/>
       </c>
     </row>
     <row r="68">
@@ -21783,9 +21387,6 @@
       <c r="C68" t="str">
         <v>GM</v>
       </c>
-      <c r="D68" t="str">
-        <v/>
-      </c>
       <c r="E68" t="str">
         <v>N.L.Meena</v>
       </c>
@@ -21797,9 +21398,6 @@
       </c>
       <c r="H68" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I68" t="str">
-        <v/>
       </c>
     </row>
     <row r="69">
@@ -21812,9 +21410,6 @@
       <c r="C69" t="str">
         <v>DGM</v>
       </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
       <c r="E69" t="str">
         <v>Umesh kumar Dua</v>
       </c>
@@ -21826,9 +21421,6 @@
       </c>
       <c r="H69" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I69" t="str">
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -21841,9 +21433,6 @@
       <c r="C70" t="str">
         <v>AD LL</v>
       </c>
-      <c r="D70" t="str">
-        <v/>
-      </c>
       <c r="E70" t="str">
         <v>B Senthil Kumar</v>
       </c>
@@ -21855,9 +21444,6 @@
       </c>
       <c r="H70" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I70" t="str">
-        <v/>
       </c>
     </row>
     <row r="71">
@@ -21870,9 +21456,6 @@
       <c r="C71" t="str">
         <v>JTO</v>
       </c>
-      <c r="D71" t="str">
-        <v/>
-      </c>
       <c r="E71" t="str">
         <v>Navdeep Garg</v>
       </c>
@@ -21884,9 +21467,6 @@
       </c>
       <c r="H71" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I71" t="str">
-        <v/>
       </c>
     </row>
     <row r="72">
@@ -21899,9 +21479,6 @@
       <c r="C72" t="str">
         <v>JE</v>
       </c>
-      <c r="D72" t="str">
-        <v/>
-      </c>
       <c r="E72" t="str">
         <v>Surjeet Singh</v>
       </c>
@@ -21913,9 +21490,6 @@
       </c>
       <c r="H72" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I72" t="str">
-        <v/>
       </c>
     </row>
     <row r="73">
@@ -21928,9 +21502,6 @@
       <c r="C73" t="str">
         <v>CGM</v>
       </c>
-      <c r="D73" t="str">
-        <v/>
-      </c>
       <c r="E73" t="str">
         <v>Saurav Tyagi</v>
       </c>
@@ -21942,9 +21513,6 @@
       </c>
       <c r="H73" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I73" t="str">
-        <v/>
       </c>
     </row>
     <row r="74">
@@ -21957,9 +21525,6 @@
       <c r="C74" t="str">
         <v>GM</v>
       </c>
-      <c r="D74" t="str">
-        <v/>
-      </c>
       <c r="E74" t="str">
         <v>NULL</v>
       </c>
@@ -21971,9 +21536,6 @@
       </c>
       <c r="H74" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I74" t="str">
-        <v/>
       </c>
     </row>
     <row r="75">
@@ -21986,9 +21548,6 @@
       <c r="C75" t="str">
         <v>DGM</v>
       </c>
-      <c r="D75" t="str">
-        <v/>
-      </c>
       <c r="E75" t="str">
         <v>AramanSharma</v>
       </c>
@@ -22000,9 +21559,6 @@
       </c>
       <c r="H75" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I75" t="str">
-        <v/>
       </c>
     </row>
     <row r="76">
@@ -22015,9 +21571,6 @@
       <c r="C76" t="str">
         <v>AD</v>
       </c>
-      <c r="D76" t="str">
-        <v/>
-      </c>
       <c r="E76" t="str">
         <v>Samir Raina</v>
       </c>
@@ -22029,9 +21582,6 @@
       </c>
       <c r="H76" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I76" t="str">
-        <v/>
       </c>
     </row>
     <row r="77">
@@ -22044,9 +21594,6 @@
       <c r="C77" t="str">
         <v>JTO</v>
       </c>
-      <c r="D77" t="str">
-        <v/>
-      </c>
       <c r="E77" t="str">
         <v>Sumanth kumar</v>
       </c>
@@ -22058,9 +21605,6 @@
       </c>
       <c r="H77" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I77" t="str">
-        <v/>
       </c>
     </row>
     <row r="78">
@@ -22073,9 +21617,6 @@
       <c r="C78" t="str">
         <v>SDE (EB/LL)</v>
       </c>
-      <c r="D78" t="str">
-        <v/>
-      </c>
       <c r="E78" t="str">
         <v>Heena Khan-srinagar ba</v>
       </c>
@@ -22087,9 +21628,6 @@
       </c>
       <c r="H78" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I78" t="str">
-        <v/>
       </c>
     </row>
     <row r="79">
@@ -22102,9 +21640,6 @@
       <c r="C79" t="str">
         <v>CGM</v>
       </c>
-      <c r="D79" t="str">
-        <v/>
-      </c>
       <c r="E79" t="str">
         <v>Ashish Kumar Das</v>
       </c>
@@ -22116,9 +21651,6 @@
       </c>
       <c r="H79" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I79" t="str">
-        <v/>
       </c>
     </row>
     <row r="80">
@@ -22131,9 +21663,6 @@
       <c r="C80" t="str">
         <v>PGM</v>
       </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
       <c r="E80" t="str">
         <v>Umesh prasad Sah</v>
       </c>
@@ -22145,9 +21674,6 @@
       </c>
       <c r="H80" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I80" t="str">
-        <v/>
       </c>
     </row>
     <row r="81">
@@ -22160,9 +21686,6 @@
       <c r="C81" t="str">
         <v>DGM</v>
       </c>
-      <c r="D81" t="str">
-        <v/>
-      </c>
       <c r="E81" t="str">
         <v>Anupam Tewan</v>
       </c>
@@ -22174,9 +21697,6 @@
       </c>
       <c r="H81" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I81" t="str">
-        <v/>
       </c>
     </row>
     <row r="82">
@@ -22189,9 +21709,6 @@
       <c r="C82" t="str">
         <v>AGM</v>
       </c>
-      <c r="D82" t="str">
-        <v/>
-      </c>
       <c r="E82" t="str">
         <v>Sanjay Kumar Poddar</v>
       </c>
@@ -22203,9 +21720,6 @@
       </c>
       <c r="H82" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I82" t="str">
-        <v/>
       </c>
     </row>
     <row r="83">
@@ -22218,9 +21732,6 @@
       <c r="C83" t="str">
         <v>AGM</v>
       </c>
-      <c r="D83" t="str">
-        <v/>
-      </c>
       <c r="E83" t="str">
         <v>Kuldeep Kumar</v>
       </c>
@@ -22232,9 +21743,6 @@
       </c>
       <c r="H83" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I83" t="str">
-        <v/>
       </c>
     </row>
     <row r="84">
@@ -22247,9 +21755,6 @@
       <c r="C84" t="str">
         <v>SDE</v>
       </c>
-      <c r="D84" t="str">
-        <v/>
-      </c>
       <c r="E84" t="str">
         <v>Vivek Kumar</v>
       </c>
@@ -22261,9 +21766,6 @@
       </c>
       <c r="H84" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I84" t="str">
-        <v/>
       </c>
     </row>
     <row r="85">
@@ -22276,9 +21778,6 @@
       <c r="C85" t="str">
         <v>JE</v>
       </c>
-      <c r="D85" t="str">
-        <v/>
-      </c>
       <c r="E85" t="str">
         <v>Vivek</v>
       </c>
@@ -22290,9 +21789,6 @@
       </c>
       <c r="H85" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I85" t="str">
-        <v/>
       </c>
     </row>
     <row r="86">
@@ -22305,9 +21801,6 @@
       <c r="C86" t="str">
         <v>CGM</v>
       </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
       <c r="E86" t="str">
         <v>N Sujatha</v>
       </c>
@@ -22319,9 +21812,6 @@
       </c>
       <c r="H86" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I86" t="str">
-        <v/>
       </c>
     </row>
     <row r="87">
@@ -22334,9 +21824,6 @@
       <c r="C87" t="str">
         <v>GM EB</v>
       </c>
-      <c r="D87" t="str">
-        <v/>
-      </c>
       <c r="E87" t="str">
         <v>Shri Arun Kumar</v>
       </c>
@@ -22348,9 +21835,6 @@
       </c>
       <c r="H87" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I87" t="str">
-        <v/>
       </c>
     </row>
     <row r="88">
@@ -22363,9 +21847,6 @@
       <c r="C88" t="str">
         <v>DGM EB CRM</v>
       </c>
-      <c r="D88" t="str">
-        <v/>
-      </c>
       <c r="E88" t="str">
         <v>Preethi</v>
       </c>
@@ -22377,9 +21858,6 @@
       </c>
       <c r="H88" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I88" t="str">
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -22392,9 +21870,6 @@
       <c r="C89" t="str">
         <v>AGM-EB CRM</v>
       </c>
-      <c r="D89" t="str">
-        <v/>
-      </c>
       <c r="E89" t="str">
         <v>Chandrasekhar</v>
       </c>
@@ -22406,9 +21881,6 @@
       </c>
       <c r="H89" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I89" t="str">
-        <v/>
       </c>
     </row>
     <row r="90">
@@ -22421,9 +21893,6 @@
       <c r="C90" t="str">
         <v>JTO-EB-CRM-SA</v>
       </c>
-      <c r="D90" t="str">
-        <v/>
-      </c>
       <c r="E90" t="str">
         <v>KISHORE.P</v>
       </c>
@@ -22435,9 +21904,6 @@
       </c>
       <c r="H90" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I90" t="str">
-        <v/>
       </c>
     </row>
     <row r="91">
@@ -22450,9 +21916,6 @@
       <c r="C91" t="str">
         <v>AGM CRM-SD(KSWAN)</v>
       </c>
-      <c r="D91" t="str">
-        <v/>
-      </c>
       <c r="E91" t="str">
         <v>Ashokshigli</v>
       </c>
@@ -22464,9 +21927,6 @@
       </c>
       <c r="H91" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I91" t="str">
-        <v/>
       </c>
     </row>
     <row r="92">
@@ -22479,9 +21939,6 @@
       <c r="C92" t="str">
         <v>SDE CRM-SD</v>
       </c>
-      <c r="D92" t="str">
-        <v/>
-      </c>
       <c r="E92" t="str">
         <v>Surya N.C</v>
       </c>
@@ -22493,9 +21950,6 @@
       </c>
       <c r="H92" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I92" t="str">
-        <v/>
       </c>
     </row>
     <row r="93">
@@ -22508,9 +21962,6 @@
       <c r="C93" t="str">
         <v>SDE CRM-SA</v>
       </c>
-      <c r="D93" t="str">
-        <v/>
-      </c>
       <c r="E93" t="str">
         <v>Balasubramanyam</v>
       </c>
@@ -22522,9 +21973,6 @@
       </c>
       <c r="H93" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I93" t="str">
-        <v/>
       </c>
     </row>
     <row r="94">
@@ -22537,9 +21985,6 @@
       <c r="C94" t="str">
         <v>JTO CRM-SD</v>
       </c>
-      <c r="D94" t="str">
-        <v/>
-      </c>
       <c r="E94" t="str">
         <v>Nityanand</v>
       </c>
@@ -22551,9 +21996,6 @@
       </c>
       <c r="H94" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I94" t="str">
-        <v/>
       </c>
     </row>
     <row r="95">
@@ -22566,9 +22008,6 @@
       <c r="C95" t="str">
         <v>SDE CRM-SA</v>
       </c>
-      <c r="D95" t="str">
-        <v/>
-      </c>
       <c r="E95" t="str">
         <v>Nareshreddy</v>
       </c>
@@ -22580,9 +22019,6 @@
       </c>
       <c r="H95" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I95" t="str">
-        <v/>
       </c>
     </row>
     <row r="96">
@@ -22595,9 +22031,6 @@
       <c r="C96" t="str">
         <v>SDE CRM-SA  JTO-94484 40555 CHitradurga</v>
       </c>
-      <c r="D96" t="str">
-        <v/>
-      </c>
       <c r="E96" t="str">
         <v>Salini Jose</v>
       </c>
@@ -22609,9 +22042,6 @@
       </c>
       <c r="H96" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I96" t="str">
-        <v/>
       </c>
     </row>
     <row r="97">
@@ -22624,9 +22054,6 @@
       <c r="C97" t="str">
         <v>JTO CRM-SA</v>
       </c>
-      <c r="D97" t="str">
-        <v/>
-      </c>
       <c r="E97" t="str">
         <v>KISHORE POOJARI</v>
       </c>
@@ -22638,9 +22065,6 @@
       </c>
       <c r="H97" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I97" t="str">
-        <v/>
       </c>
     </row>
     <row r="98">
@@ -22653,9 +22077,6 @@
       <c r="C98" t="str">
         <v>CGM</v>
       </c>
-      <c r="D98" t="str">
-        <v/>
-      </c>
       <c r="E98" t="str">
         <v>Shri. B SUNIL KUMAR</v>
       </c>
@@ -22667,9 +22088,6 @@
       </c>
       <c r="H98" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I98" t="str">
-        <v/>
       </c>
     </row>
     <row r="99">
@@ -22682,9 +22100,6 @@
       <c r="C99" t="str">
         <v>PGM EB</v>
       </c>
-      <c r="D99" t="str">
-        <v/>
-      </c>
       <c r="E99" t="str">
         <v>Shri. Nirmal P G</v>
       </c>
@@ -22696,9 +22111,6 @@
       </c>
       <c r="H99" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I99" t="str">
-        <v/>
       </c>
     </row>
     <row r="100">
@@ -22711,9 +22123,6 @@
       <c r="C100" t="str">
         <v>DGM EB</v>
       </c>
-      <c r="D100" t="str">
-        <v/>
-      </c>
       <c r="E100" t="str">
         <v>Smt Ezhil Simon</v>
       </c>
@@ -22725,9 +22134,6 @@
       </c>
       <c r="H100" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I100" t="str">
-        <v/>
       </c>
     </row>
     <row r="101">
@@ -22740,9 +22146,6 @@
       <c r="C101" t="str">
         <v>AGM EB CRM</v>
       </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
       <c r="E101" t="str">
         <v>Aneetha M</v>
       </c>
@@ -22754,9 +22157,6 @@
       </c>
       <c r="H101" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I101" t="str">
-        <v/>
       </c>
     </row>
     <row r="102">
@@ -22769,9 +22169,6 @@
       <c r="C102" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
       <c r="E102" t="str">
         <v>Arun S Jyothi</v>
       </c>
@@ -22783,9 +22180,6 @@
       </c>
       <c r="H102" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I102" t="str">
-        <v/>
       </c>
     </row>
     <row r="103">
@@ -22798,9 +22192,6 @@
       <c r="C103" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
       <c r="E103" t="str">
         <v>ANSAL J</v>
       </c>
@@ -22812,9 +22203,6 @@
       </c>
       <c r="H103" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I103" t="str">
-        <v/>
       </c>
     </row>
     <row r="104">
@@ -22827,9 +22215,6 @@
       <c r="C104" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D104" t="str">
-        <v/>
-      </c>
       <c r="E104" t="str">
         <v>MAXMILAN K</v>
       </c>
@@ -22841,9 +22226,6 @@
       </c>
       <c r="H104" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I104" t="str">
-        <v/>
       </c>
     </row>
     <row r="105">
@@ -22856,9 +22238,6 @@
       <c r="C105" t="str">
         <v>SDE CRM</v>
       </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
       <c r="E105" t="str">
         <v>VINI JOSEPH</v>
       </c>
@@ -22870,9 +22249,6 @@
       </c>
       <c r="H105" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I105" t="str">
-        <v/>
       </c>
     </row>
     <row r="106">
@@ -22885,9 +22261,6 @@
       <c r="C106" t="str">
         <v>JTO CRM</v>
       </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
       <c r="E106" t="str">
         <v>VINITHA A</v>
       </c>
@@ -22899,9 +22272,6 @@
       </c>
       <c r="H106" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I106" t="str">
-        <v/>
       </c>
     </row>
     <row r="107">
@@ -22914,9 +22284,6 @@
       <c r="C107" t="str">
         <v>CGM CTD</v>
       </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
       <c r="E107" t="str">
         <v>D.C.Tikadar</v>
       </c>
@@ -22928,9 +22295,6 @@
       </c>
       <c r="H107" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I107" t="str">
-        <v/>
       </c>
     </row>
     <row r="108">
@@ -22943,9 +22307,6 @@
       <c r="C108" t="str">
         <v>GM EB CTD</v>
       </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
       <c r="E108" t="str">
         <v>Kaushik Mukherjee</v>
       </c>
@@ -22957,9 +22318,6 @@
       </c>
       <c r="H108" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I108" t="str">
-        <v/>
       </c>
     </row>
     <row r="109">
@@ -22972,9 +22330,6 @@
       <c r="C109" t="str">
         <v>DGM/CRM/LC,CTD</v>
       </c>
-      <c r="D109" t="str">
-        <v/>
-      </c>
       <c r="E109" t="str">
         <v>Biswarup Mandal</v>
       </c>
@@ -22986,9 +22341,6 @@
       </c>
       <c r="H109" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I109" t="str">
-        <v/>
       </c>
     </row>
     <row r="110">
@@ -23001,9 +22353,6 @@
       <c r="C110" t="str">
         <v>DE/CRM-I</v>
       </c>
-      <c r="D110" t="str">
-        <v/>
-      </c>
       <c r="E110" t="str">
         <v>Niren Kumar</v>
       </c>
@@ -23015,9 +22364,6 @@
       </c>
       <c r="H110" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I110" t="str">
-        <v/>
       </c>
     </row>
     <row r="111">
@@ -23030,9 +22376,6 @@
       <c r="C111" t="str">
         <v>SDE/CRM-I CRM-I</v>
       </c>
-      <c r="D111" t="str">
-        <v/>
-      </c>
       <c r="E111" t="str">
         <v>Bikas Shekhar</v>
       </c>
@@ -23044,9 +22387,6 @@
       </c>
       <c r="H111" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I111" t="str">
-        <v/>
       </c>
     </row>
     <row r="112">
@@ -23059,9 +22399,6 @@
       <c r="C112" t="str">
         <v>SDE/CRM-I CRM-I</v>
       </c>
-      <c r="D112" t="str">
-        <v/>
-      </c>
       <c r="E112" t="str">
         <v>Paromita Mandal</v>
       </c>
@@ -23073,9 +22410,6 @@
       </c>
       <c r="H112" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I112" t="str">
-        <v/>
       </c>
     </row>
     <row r="113">
@@ -23088,9 +22422,6 @@
       <c r="C113" t="str">
         <v>JTO/CRM-I CRM-I</v>
       </c>
-      <c r="D113" t="str">
-        <v/>
-      </c>
       <c r="E113" t="str">
         <v>Dhiraj Kumar Jha</v>
       </c>
@@ -23102,9 +22433,6 @@
       </c>
       <c r="H113" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I113" t="str">
-        <v/>
       </c>
     </row>
     <row r="114">
@@ -23117,9 +22445,6 @@
       <c r="C114" t="str">
         <v>JTO/CRM-I CRM-I</v>
       </c>
-      <c r="D114" t="str">
-        <v/>
-      </c>
       <c r="E114" t="str">
         <v>Sanjoy Das</v>
       </c>
@@ -23131,9 +22456,6 @@
       </c>
       <c r="H114" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I114" t="str">
-        <v/>
       </c>
     </row>
     <row r="115">
@@ -23146,9 +22468,6 @@
       <c r="C115" t="str">
         <v>JTO/CRM-I CRM-I</v>
       </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
       <c r="E115" t="str">
         <v>Bhajan Roy</v>
       </c>
@@ -23160,9 +22479,6 @@
       </c>
       <c r="H115" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I115" t="str">
-        <v/>
       </c>
     </row>
     <row r="116">
@@ -23175,9 +22491,6 @@
       <c r="C116" t="str">
         <v>AGM/NIB</v>
       </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
       <c r="E116" t="str">
         <v>Shyam Hembram</v>
       </c>
@@ -23189,9 +22502,6 @@
       </c>
       <c r="H116" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I116" t="str">
-        <v/>
       </c>
     </row>
     <row r="117">
@@ -23204,9 +22514,6 @@
       <c r="C117" t="str">
         <v>AGM/Commercial</v>
       </c>
-      <c r="D117" t="str">
-        <v/>
-      </c>
       <c r="E117" t="str">
         <v>Indrajeet Kumar</v>
       </c>
@@ -23218,9 +22525,6 @@
       </c>
       <c r="H117" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I117" t="str">
-        <v/>
       </c>
     </row>
     <row r="118">
@@ -23233,9 +22537,6 @@
       <c r="C118" t="str">
         <v>AGM/SA/IG/CTD</v>
       </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
       <c r="E118" t="str">
         <v>Sri Sadhan Chandra Mandal</v>
       </c>
@@ -23247,9 +22548,6 @@
       </c>
       <c r="H118" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I118" t="str">
-        <v/>
       </c>
     </row>
     <row r="119">
@@ -23262,9 +22560,6 @@
       <c r="C119" t="str">
         <v>AGM/SD/CTD</v>
       </c>
-      <c r="D119" t="str">
-        <v/>
-      </c>
       <c r="E119" t="str">
         <v>Sri Asheesh Kumar Gupta</v>
       </c>
@@ -23276,9 +22571,6 @@
       </c>
       <c r="H119" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I119" t="str">
-        <v/>
       </c>
     </row>
     <row r="120">
@@ -23291,9 +22583,6 @@
       <c r="C120" t="str">
         <v>SDE Commercial EB</v>
       </c>
-      <c r="D120" t="str">
-        <v/>
-      </c>
       <c r="E120" t="str">
         <v>Mukesh Singh</v>
       </c>
@@ -23305,9 +22594,6 @@
       </c>
       <c r="H120" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I120" t="str">
-        <v/>
       </c>
     </row>
     <row r="121">
@@ -23320,9 +22606,6 @@
       <c r="C121" t="str">
         <v>SDE/SD/CTD</v>
       </c>
-      <c r="D121" t="str">
-        <v/>
-      </c>
       <c r="E121" t="str">
         <v>SAURABH HALDER</v>
       </c>
@@ -23334,9 +22617,6 @@
       </c>
       <c r="H121" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I121" t="str">
-        <v/>
       </c>
     </row>
     <row r="122">
@@ -23349,9 +22629,6 @@
       <c r="C122" t="str">
         <v>JE/CRM-II CRM-II</v>
       </c>
-      <c r="D122" t="str">
-        <v/>
-      </c>
       <c r="E122" t="str">
         <v>Abhiram Mahto</v>
       </c>
@@ -23363,9 +22640,6 @@
       </c>
       <c r="H122" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I122" t="str">
-        <v/>
       </c>
     </row>
     <row r="123">
@@ -23378,9 +22652,6 @@
       <c r="C123" t="str">
         <v>JE/CRM-II CRM-II</v>
       </c>
-      <c r="D123" t="str">
-        <v/>
-      </c>
       <c r="E123" t="str">
         <v>Soma Choudhury</v>
       </c>
@@ -23392,9 +22663,6 @@
       </c>
       <c r="H123" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I123" t="str">
-        <v/>
       </c>
     </row>
     <row r="124">
@@ -23407,9 +22675,6 @@
       <c r="C124" t="str">
         <v>SDE/SA NIB</v>
       </c>
-      <c r="D124" t="str">
-        <v/>
-      </c>
       <c r="E124" t="str">
         <v>Arunava Mandal</v>
       </c>
@@ -23421,9 +22686,6 @@
       </c>
       <c r="H124" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I124" t="str">
-        <v/>
       </c>
     </row>
     <row r="125">
@@ -23436,9 +22698,6 @@
       <c r="C125" t="str">
         <v>JTO/SA NIB</v>
       </c>
-      <c r="D125" t="str">
-        <v/>
-      </c>
       <c r="E125" t="str">
         <v>Arup Santra</v>
       </c>
@@ -23450,9 +22709,6 @@
       </c>
       <c r="H125" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I125" t="str">
-        <v/>
       </c>
     </row>
     <row r="126">
@@ -23465,9 +22721,6 @@
       <c r="C126" t="str">
         <v>JTO/SA&amp;SD NIB</v>
       </c>
-      <c r="D126" t="str">
-        <v/>
-      </c>
       <c r="E126" t="str">
         <v>Sandip Das</v>
       </c>
@@ -23479,9 +22732,6 @@
       </c>
       <c r="H126" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I126" t="str">
-        <v/>
       </c>
     </row>
     <row r="127">
@@ -23494,9 +22744,6 @@
       <c r="C127" t="str">
         <v>JTO/SA NIB</v>
       </c>
-      <c r="D127" t="str">
-        <v/>
-      </c>
       <c r="E127" t="str">
         <v>ABHA BHARTI</v>
       </c>
@@ -23508,9 +22755,6 @@
       </c>
       <c r="H127" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I127" t="str">
-        <v/>
       </c>
     </row>
     <row r="128">
@@ -23523,9 +22767,6 @@
       <c r="C128" t="str">
         <v>JTO/SA NIB</v>
       </c>
-      <c r="D128" t="str">
-        <v/>
-      </c>
       <c r="E128" t="str">
         <v>Sujoy Kumar Mahinder</v>
       </c>
@@ -23537,9 +22778,6 @@
       </c>
       <c r="H128" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I128" t="str">
-        <v/>
       </c>
     </row>
     <row r="129">
@@ -23552,9 +22790,6 @@
       <c r="C129" t="str">
         <v>JTO/SA&amp;SD NIB</v>
       </c>
-      <c r="D129" t="str">
-        <v/>
-      </c>
       <c r="E129" t="str">
         <v>AMIT KUMAR KOLEY</v>
       </c>
@@ -23566,9 +22801,6 @@
       </c>
       <c r="H129" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I129" t="str">
-        <v/>
       </c>
     </row>
     <row r="130">
@@ -23581,9 +22813,6 @@
       <c r="C130" t="str">
         <v>JTO/SD NIB</v>
       </c>
-      <c r="D130" t="str">
-        <v/>
-      </c>
       <c r="E130" t="str">
         <v>AMIT KUMAR DE</v>
       </c>
@@ -23595,9 +22824,6 @@
       </c>
       <c r="H130" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I130" t="str">
-        <v/>
       </c>
     </row>
     <row r="131">
@@ -23610,9 +22836,6 @@
       <c r="C131" t="str">
         <v>JTO/SD NIB</v>
       </c>
-      <c r="D131" t="str">
-        <v/>
-      </c>
       <c r="E131" t="str">
         <v>Himangu Das</v>
       </c>
@@ -23624,9 +22847,6 @@
       </c>
       <c r="H131" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I131" t="str">
-        <v/>
       </c>
     </row>
     <row r="132">
@@ -23639,9 +22859,6 @@
       <c r="C132" t="str">
         <v>JTO/SD/CTD</v>
       </c>
-      <c r="D132" t="str">
-        <v/>
-      </c>
       <c r="E132" t="str">
         <v>Vijaya Laxmi</v>
       </c>
@@ -23653,9 +22870,6 @@
       </c>
       <c r="H132" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I132" t="str">
-        <v/>
       </c>
     </row>
     <row r="133">
@@ -23668,9 +22882,6 @@
       <c r="C133" t="str">
         <v>JE/SA NIB</v>
       </c>
-      <c r="D133" t="str">
-        <v/>
-      </c>
       <c r="E133" t="str">
         <v>Jyotindra Nath Chakraborty</v>
       </c>
@@ -23682,9 +22893,6 @@
       </c>
       <c r="H133" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I133" t="str">
-        <v/>
       </c>
     </row>
     <row r="134">
@@ -23697,9 +22905,6 @@
       <c r="C134" t="str">
         <v>JE/SA NIB</v>
       </c>
-      <c r="D134" t="str">
-        <v/>
-      </c>
       <c r="E134" t="str">
         <v>Biswajit Sarkar</v>
       </c>
@@ -23711,9 +22916,6 @@
       </c>
       <c r="H134" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I134" t="str">
-        <v/>
       </c>
     </row>
     <row r="135">
@@ -23726,9 +22928,6 @@
       <c r="C135" t="str">
         <v>CGMT</v>
       </c>
-      <c r="D135" t="str">
-        <v/>
-      </c>
       <c r="E135" t="str">
         <v>Shri HARINDER KUMAR</v>
       </c>
@@ -23740,9 +22939,6 @@
       </c>
       <c r="H135" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I135" t="str">
-        <v/>
       </c>
     </row>
     <row r="136">
@@ -23755,9 +22951,6 @@
       <c r="C136" t="str">
         <v>GM EB MBI</v>
       </c>
-      <c r="D136" t="str">
-        <v/>
-      </c>
       <c r="E136" t="str">
         <v>Shri Jayen Sao</v>
       </c>
@@ -23769,9 +22962,6 @@
       </c>
       <c r="H136" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I136" t="str">
-        <v/>
       </c>
     </row>
     <row r="137">
@@ -23784,9 +22974,6 @@
       <c r="C137" t="str">
         <v>PA to GM (EB-Platinum)</v>
       </c>
-      <c r="D137" t="str">
-        <v/>
-      </c>
       <c r="E137" t="str">
         <v>Rajasi Pai</v>
       </c>
@@ -23798,9 +22985,6 @@
       </c>
       <c r="H137" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I137" t="str">
-        <v/>
       </c>
     </row>
     <row r="138">
@@ -23813,9 +22997,6 @@
       <c r="C138" t="str">
         <v>DGM(EB)</v>
       </c>
-      <c r="D138" t="str">
-        <v/>
-      </c>
       <c r="E138" t="str">
         <v>V B Kokate</v>
       </c>
@@ -23827,9 +23008,6 @@
       </c>
       <c r="H138" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I138" t="str">
-        <v/>
       </c>
     </row>
     <row r="139">
@@ -23842,9 +23020,6 @@
       <c r="C139" t="str">
         <v>DGM(EB)</v>
       </c>
-      <c r="D139" t="str">
-        <v/>
-      </c>
       <c r="E139" t="str">
         <v>P.R.Desai</v>
       </c>
@@ -23856,9 +23031,6 @@
       </c>
       <c r="H139" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I139" t="str">
-        <v/>
       </c>
     </row>
     <row r="140">
@@ -23871,9 +23043,6 @@
       <c r="C140" t="str">
         <v>AGM EB CRM</v>
       </c>
-      <c r="D140" t="str">
-        <v/>
-      </c>
       <c r="E140" t="str">
         <v>Shubhada Raspayle</v>
       </c>
@@ -23885,9 +23054,6 @@
       </c>
       <c r="H140" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I140" t="str">
-        <v/>
       </c>
     </row>
     <row r="141">
@@ -23900,9 +23066,6 @@
       <c r="C141" t="str">
         <v>AGM EB CRM</v>
       </c>
-      <c r="D141" t="str">
-        <v/>
-      </c>
       <c r="E141" t="str">
         <v>Bhavesh Joshi</v>
       </c>
@@ -23914,9 +23077,6 @@
       </c>
       <c r="H141" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I141" t="str">
-        <v/>
       </c>
     </row>
     <row r="142">
@@ -23929,9 +23089,6 @@
       <c r="C142" t="str">
         <v>AGM EB CRM</v>
       </c>
-      <c r="D142" t="str">
-        <v/>
-      </c>
       <c r="E142" t="str">
         <v>Ajaykumar Vasani</v>
       </c>
@@ -23943,9 +23100,6 @@
       </c>
       <c r="H142" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I142" t="str">
-        <v/>
       </c>
     </row>
     <row r="143">
@@ -23958,9 +23112,6 @@
       <c r="C143" t="str">
         <v>AGM EB CRM</v>
       </c>
-      <c r="D143" t="str">
-        <v/>
-      </c>
       <c r="E143" t="str">
         <v>Sanjaykumar R Patel</v>
       </c>
@@ -23972,9 +23123,6 @@
       </c>
       <c r="H143" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I143" t="str">
-        <v/>
       </c>
     </row>
     <row r="144">
@@ -23987,9 +23135,6 @@
       <c r="C144" t="str">
         <v>AD(EB-CO)</v>
       </c>
-      <c r="D144" t="str">
-        <v/>
-      </c>
       <c r="E144" t="str">
         <v>Vishal Motghare</v>
       </c>
@@ -24001,9 +23146,6 @@
       </c>
       <c r="H144" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I144" t="str">
-        <v/>
       </c>
     </row>
     <row r="145">
@@ -24016,9 +23158,6 @@
       <c r="C145" t="str">
         <v>AD EB CO4</v>
       </c>
-      <c r="D145" t="str">
-        <v/>
-      </c>
       <c r="E145" t="str">
         <v>Chate Laxman V</v>
       </c>
@@ -24030,9 +23169,6 @@
       </c>
       <c r="H145" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I145" t="str">
-        <v/>
       </c>
     </row>
     <row r="146">
@@ -24045,9 +23181,6 @@
       <c r="C146" t="str">
         <v>AD EB Sales</v>
       </c>
-      <c r="D146" t="str">
-        <v/>
-      </c>
       <c r="E146" t="str">
         <v>Nikki Jagwani</v>
       </c>
@@ -24059,9 +23192,6 @@
       </c>
       <c r="H146" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I146" t="str">
-        <v/>
       </c>
     </row>
     <row r="147">
@@ -24074,9 +23204,6 @@
       <c r="C147" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D147" t="str">
-        <v/>
-      </c>
       <c r="E147" t="str">
         <v>Pankaj Patil</v>
       </c>
@@ -24088,9 +23215,6 @@
       </c>
       <c r="H147" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I147" t="str">
-        <v/>
       </c>
     </row>
     <row r="148">
@@ -24103,9 +23227,6 @@
       <c r="C148" t="str">
         <v>AD EB preSales</v>
       </c>
-      <c r="D148" t="str">
-        <v/>
-      </c>
       <c r="E148" t="str">
         <v>Sankalp Sawant</v>
       </c>
@@ -24117,9 +23238,6 @@
       </c>
       <c r="H148" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I148" t="str">
-        <v/>
       </c>
     </row>
     <row r="149">
@@ -24132,9 +23250,6 @@
       <c r="C149" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D149" t="str">
-        <v/>
-      </c>
       <c r="E149" t="str">
         <v>Himanshu Bhagul</v>
       </c>
@@ -24146,9 +23261,6 @@
       </c>
       <c r="H149" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I149" t="str">
-        <v/>
       </c>
     </row>
     <row r="150">
@@ -24161,9 +23273,6 @@
       <c r="C150" t="str">
         <v>AD EB Sales</v>
       </c>
-      <c r="D150" t="str">
-        <v/>
-      </c>
       <c r="E150" t="str">
         <v>Mukesh Wadhavani</v>
       </c>
@@ -24175,9 +23284,6 @@
       </c>
       <c r="H150" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I150" t="str">
-        <v/>
       </c>
     </row>
     <row r="151">
@@ -24190,9 +23296,6 @@
       <c r="C151" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D151" t="str">
-        <v/>
-      </c>
       <c r="E151" t="str">
         <v>Deepak T K</v>
       </c>
@@ -24204,9 +23307,6 @@
       </c>
       <c r="H151" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I151" t="str">
-        <v/>
       </c>
     </row>
     <row r="152">
@@ -24219,9 +23319,6 @@
       <c r="C152" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D152" t="str">
-        <v/>
-      </c>
       <c r="E152" t="str">
         <v>Shivani Saini</v>
       </c>
@@ -24233,9 +23330,6 @@
       </c>
       <c r="H152" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I152" t="str">
-        <v/>
       </c>
     </row>
     <row r="153">
@@ -24248,9 +23342,6 @@
       <c r="C153" t="str">
         <v>SDE EB CRM</v>
       </c>
-      <c r="D153" t="str">
-        <v/>
-      </c>
       <c r="E153" t="str">
         <v>Ravi Khant Srivastava</v>
       </c>
@@ -24262,9 +23353,6 @@
       </c>
       <c r="H153" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I153" t="str">
-        <v/>
       </c>
     </row>
     <row r="154">
@@ -24277,9 +23365,6 @@
       <c r="C154" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D154" t="str">
-        <v/>
-      </c>
       <c r="E154" t="str">
         <v>Amisha Kamdar</v>
       </c>
@@ -24291,9 +23376,6 @@
       </c>
       <c r="H154" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I154" t="str">
-        <v/>
       </c>
     </row>
     <row r="155">
@@ -24306,9 +23388,6 @@
       <c r="C155" t="str">
         <v>JTO EB CRM</v>
       </c>
-      <c r="D155" t="str">
-        <v/>
-      </c>
       <c r="E155" t="str">
         <v>BHAGWANDAS MANGHANI</v>
       </c>
@@ -24320,9 +23399,6 @@
       </c>
       <c r="H155" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I155" t="str">
-        <v/>
       </c>
     </row>
     <row r="156">
@@ -24335,9 +23411,6 @@
       <c r="C156" t="str">
         <v>JAO(EB-Comm)</v>
       </c>
-      <c r="D156" t="str">
-        <v/>
-      </c>
       <c r="E156" t="str">
         <v>Mohan Lal Soni</v>
       </c>
@@ -24349,9 +23422,6 @@
       </c>
       <c r="H156" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I156" t="str">
-        <v/>
       </c>
     </row>
     <row r="157">
@@ -24364,9 +23434,6 @@
       <c r="C157" t="str">
         <v>JTO</v>
       </c>
-      <c r="D157" t="str">
-        <v/>
-      </c>
       <c r="E157" t="str">
         <v>Pratibha Saraf</v>
       </c>
@@ -24378,9 +23445,6 @@
       </c>
       <c r="H157" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I157" t="str">
-        <v/>
       </c>
     </row>
     <row r="158">
@@ -24393,9 +23457,6 @@
       <c r="C158" t="str">
         <v>SDE Commercial EB</v>
       </c>
-      <c r="D158" t="str">
-        <v/>
-      </c>
       <c r="E158" t="str">
         <v>Vishal Motghare</v>
       </c>
@@ -24407,9 +23468,6 @@
       </c>
       <c r="H158" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I158" t="str">
-        <v/>
       </c>
     </row>
     <row r="159">
@@ -24422,9 +23480,6 @@
       <c r="C159" t="str">
         <v>SDE Commercial EB</v>
       </c>
-      <c r="D159" t="str">
-        <v/>
-      </c>
       <c r="E159" t="str">
         <v>Shaila Khadgi</v>
       </c>
@@ -24436,9 +23491,6 @@
       </c>
       <c r="H159" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I159" t="str">
-        <v/>
       </c>
     </row>
     <row r="160">
@@ -24451,9 +23503,6 @@
       <c r="C160" t="str">
         <v>SDE EB Post Sales</v>
       </c>
-      <c r="D160" t="str">
-        <v/>
-      </c>
       <c r="E160" t="str">
         <v>Yogesh Patel</v>
       </c>
@@ -24465,9 +23514,6 @@
       </c>
       <c r="H160" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I160" t="str">
-        <v/>
       </c>
     </row>
     <row r="161">
@@ -24480,9 +23526,6 @@
       <c r="C161" t="str">
         <v>Sr. GM</v>
       </c>
-      <c r="D161" t="str">
-        <v/>
-      </c>
       <c r="E161" t="str">
         <v>Suhas Mankar</v>
       </c>
@@ -24494,9 +23537,6 @@
       </c>
       <c r="H161" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I161" t="str">
-        <v/>
       </c>
     </row>
     <row r="162">
@@ -24509,9 +23549,6 @@
       <c r="C162" t="str">
         <v>AGM</v>
       </c>
-      <c r="D162" t="str">
-        <v/>
-      </c>
       <c r="E162" t="str">
         <v>Yogesh Goshwami</v>
       </c>
@@ -24523,9 +23560,6 @@
       </c>
       <c r="H162" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I162" t="str">
-        <v/>
       </c>
     </row>
     <row r="163">
@@ -24538,9 +23572,6 @@
       <c r="C163" t="str">
         <v>AD</v>
       </c>
-      <c r="D163" t="str">
-        <v/>
-      </c>
       <c r="E163" t="str">
         <v>Anil Kumar Kusawaha</v>
       </c>
@@ -24552,9 +23583,6 @@
       </c>
       <c r="H163" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I163" t="str">
-        <v/>
       </c>
     </row>
     <row r="164">
@@ -24567,9 +23595,6 @@
       <c r="C164" t="str">
         <v>JTO</v>
       </c>
-      <c r="D164" t="str">
-        <v/>
-      </c>
       <c r="E164" t="str">
         <v>Suhail Akhtar</v>
       </c>
@@ -24581,9 +23606,6 @@
       </c>
       <c r="H164" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I164" t="str">
-        <v/>
       </c>
     </row>
     <row r="165">
@@ -24596,9 +23618,6 @@
       <c r="C165" t="str">
         <v>JTO</v>
       </c>
-      <c r="D165" t="str">
-        <v/>
-      </c>
       <c r="E165" t="str">
         <v>Pravin Koli</v>
       </c>
@@ -24610,9 +23629,6 @@
       </c>
       <c r="H165" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I165" t="str">
-        <v/>
       </c>
     </row>
     <row r="166">
@@ -24625,9 +23641,6 @@
       <c r="C166" t="str">
         <v>JTO</v>
       </c>
-      <c r="D166" t="str">
-        <v/>
-      </c>
       <c r="E166" t="str">
         <v>Vikas Y Bhise</v>
       </c>
@@ -24639,9 +23652,6 @@
       </c>
       <c r="H166" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I166" t="str">
-        <v/>
       </c>
     </row>
     <row r="167">
@@ -24654,9 +23664,6 @@
       <c r="C167" t="str">
         <v>JE</v>
       </c>
-      <c r="D167" t="str">
-        <v/>
-      </c>
       <c r="E167" t="str">
         <v>Priyanka Jha Lc Mh</v>
       </c>
@@ -24668,9 +23675,6 @@
       </c>
       <c r="H167" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I167" t="str">
-        <v/>
       </c>
     </row>
     <row r="168">
@@ -24683,9 +23687,6 @@
       <c r="C168" t="str">
         <v>JE</v>
       </c>
-      <c r="D168" t="str">
-        <v/>
-      </c>
       <c r="E168" t="str">
         <v>Pankaj Bhalerao</v>
       </c>
@@ -24697,9 +23698,6 @@
       </c>
       <c r="H168" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I168" t="str">
-        <v/>
       </c>
     </row>
     <row r="169">
@@ -24712,9 +23710,6 @@
       <c r="C169" t="str">
         <v>CGM</v>
       </c>
-      <c r="D169" t="str">
-        <v/>
-      </c>
       <c r="E169" t="str">
         <v>Radheshyam Parmar</v>
       </c>
@@ -24726,9 +23721,6 @@
       </c>
       <c r="H169" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I169" t="str">
-        <v/>
       </c>
     </row>
     <row r="170">
@@ -24741,9 +23733,6 @@
       <c r="C170" t="str">
         <v>PGM EB</v>
       </c>
-      <c r="D170" t="str">
-        <v/>
-      </c>
       <c r="E170" t="str">
         <v>Arun Kumar</v>
       </c>
@@ -24755,9 +23744,6 @@
       </c>
       <c r="H170" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I170" t="str">
-        <v/>
       </c>
     </row>
     <row r="171">
@@ -24770,9 +23756,6 @@
       <c r="C171" t="str">
         <v>DGM</v>
       </c>
-      <c r="D171" t="str">
-        <v/>
-      </c>
       <c r="E171" t="str">
         <v>V K Singh</v>
       </c>
@@ -24784,9 +23767,6 @@
       </c>
       <c r="H171" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I171" t="str">
-        <v/>
       </c>
     </row>
     <row r="172">
@@ -24799,9 +23779,6 @@
       <c r="C172" t="str">
         <v>AGM</v>
       </c>
-      <c r="D172" t="str">
-        <v/>
-      </c>
       <c r="E172" t="str">
         <v>S B Choudhary</v>
       </c>
@@ -24813,9 +23790,6 @@
       </c>
       <c r="H172" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I172" t="str">
-        <v/>
       </c>
     </row>
     <row r="173">
@@ -24828,9 +23802,6 @@
       <c r="C173" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D173" t="str">
-        <v/>
-      </c>
       <c r="E173" t="str">
         <v>Pradeep Kumar Gupta</v>
       </c>
@@ -24842,9 +23813,6 @@
       </c>
       <c r="H173" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I173" t="str">
-        <v/>
       </c>
     </row>
     <row r="174">
@@ -24857,9 +23825,6 @@
       <c r="C174" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D174" t="str">
-        <v/>
-      </c>
       <c r="E174" t="str">
         <v>Rajendra Parsendiya</v>
       </c>
@@ -24871,9 +23836,6 @@
       </c>
       <c r="H174" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I174" t="str">
-        <v/>
       </c>
     </row>
     <row r="175">
@@ -24886,9 +23848,6 @@
       <c r="C175" t="str">
         <v>AGM</v>
       </c>
-      <c r="D175" t="str">
-        <v/>
-      </c>
       <c r="E175" t="str">
         <v>Manish Soni</v>
       </c>
@@ -24900,9 +23859,6 @@
       </c>
       <c r="H175" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I175" t="str">
-        <v/>
       </c>
     </row>
     <row r="176">
@@ -24915,9 +23871,6 @@
       <c r="C176" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D176" t="str">
-        <v/>
-      </c>
       <c r="E176" t="str">
         <v>Sheeraz Qureshi</v>
       </c>
@@ -24929,9 +23882,6 @@
       </c>
       <c r="H176" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I176" t="str">
-        <v/>
       </c>
     </row>
     <row r="177">
@@ -24944,9 +23894,6 @@
       <c r="C177" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D177" t="str">
-        <v/>
-      </c>
       <c r="E177" t="str">
         <v>P K Jha</v>
       </c>
@@ -24958,9 +23905,6 @@
       </c>
       <c r="H177" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I177" t="str">
-        <v/>
       </c>
     </row>
     <row r="178">
@@ -24973,9 +23917,6 @@
       <c r="C178" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D178" t="str">
-        <v/>
-      </c>
       <c r="E178" t="str">
         <v>AJAY SHUKLA</v>
       </c>
@@ -24987,9 +23928,6 @@
       </c>
       <c r="H178" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I178" t="str">
-        <v/>
       </c>
     </row>
     <row r="179">
@@ -25002,9 +23940,6 @@
       <c r="C179" t="str">
         <v>SDE LC</v>
       </c>
-      <c r="D179" t="str">
-        <v/>
-      </c>
       <c r="E179" t="str">
         <v>D K SOMKUNWAR</v>
       </c>
@@ -25016,9 +23951,6 @@
       </c>
       <c r="H179" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I179" t="str">
-        <v/>
       </c>
     </row>
     <row r="180">
@@ -25031,9 +23963,6 @@
       <c r="C180" t="str">
         <v>CGM</v>
       </c>
-      <c r="D180" t="str">
-        <v/>
-      </c>
       <c r="E180" t="str">
         <v>Daily Giri</v>
       </c>
@@ -25045,9 +23974,6 @@
       </c>
       <c r="H180" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I180" t="str">
-        <v/>
       </c>
     </row>
     <row r="181">
@@ -25060,9 +23986,6 @@
       <c r="C181" t="str">
         <v>GM(EB)</v>
       </c>
-      <c r="D181" t="str">
-        <v/>
-      </c>
       <c r="E181" t="str">
         <v>Lal Hmachhuana</v>
       </c>
@@ -25074,9 +23997,6 @@
       </c>
       <c r="H181" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I181" t="str">
-        <v/>
       </c>
     </row>
     <row r="182">
@@ -25089,9 +24009,6 @@
       <c r="C182" t="str">
         <v>AGM EB</v>
       </c>
-      <c r="D182" t="str">
-        <v/>
-      </c>
       <c r="E182" t="str">
         <v>Soumen Roy</v>
       </c>
@@ -25103,9 +24020,6 @@
       </c>
       <c r="H182" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I182" t="str">
-        <v/>
       </c>
     </row>
     <row r="183">
@@ -25118,9 +24032,6 @@
       <c r="C183" t="str">
         <v>AGM</v>
       </c>
-      <c r="D183" t="str">
-        <v/>
-      </c>
       <c r="E183" t="str">
         <v>Nylla Darika Lyngdoh Nongbri</v>
       </c>
@@ -25132,9 +24043,6 @@
       </c>
       <c r="H183" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I183" t="str">
-        <v/>
       </c>
     </row>
     <row r="184">
@@ -25147,9 +24055,6 @@
       <c r="C184" t="str">
         <v>SDE(EB)</v>
       </c>
-      <c r="D184" t="str">
-        <v/>
-      </c>
       <c r="E184" t="str">
         <v>RAKESH KUMAR SHARMA</v>
       </c>
@@ -25161,9 +24066,6 @@
       </c>
       <c r="H184" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I184" t="str">
-        <v/>
       </c>
     </row>
     <row r="185">
@@ -25176,9 +24078,6 @@
       <c r="C185" t="str">
         <v>CGM</v>
       </c>
-      <c r="D185" t="str">
-        <v/>
-      </c>
       <c r="E185" t="str">
         <v>N Murali</v>
       </c>
@@ -25190,9 +24089,6 @@
       </c>
       <c r="H185" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I185" t="str">
-        <v/>
       </c>
     </row>
     <row r="186">
@@ -25205,9 +24101,6 @@
       <c r="C186" t="str">
         <v>GM</v>
       </c>
-      <c r="D186" t="str">
-        <v/>
-      </c>
       <c r="E186" t="str">
         <v>Mukesh Meena</v>
       </c>
@@ -25219,9 +24112,6 @@
       </c>
       <c r="H186" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I186" t="str">
-        <v/>
       </c>
     </row>
     <row r="187">
@@ -25234,9 +24124,6 @@
       <c r="C187" t="str">
         <v>DGM</v>
       </c>
-      <c r="D187" t="str">
-        <v/>
-      </c>
       <c r="E187" t="str">
         <v>Y R Gudhe</v>
       </c>
@@ -25248,9 +24135,6 @@
       </c>
       <c r="H187" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I187" t="str">
-        <v/>
       </c>
     </row>
     <row r="188">
@@ -25263,9 +24147,6 @@
       <c r="C188" t="str">
         <v>SDE (EB)</v>
       </c>
-      <c r="D188" t="str">
-        <v/>
-      </c>
       <c r="E188" t="str">
         <v>Puzeto Puyo</v>
       </c>
@@ -25277,9 +24158,6 @@
       </c>
       <c r="H188" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I188" t="str">
-        <v/>
       </c>
     </row>
     <row r="189">
@@ -25292,9 +24170,6 @@
       <c r="C189" t="str">
         <v>AGM</v>
       </c>
-      <c r="D189" t="str">
-        <v/>
-      </c>
       <c r="E189" t="str">
         <v>Dilip Kalita</v>
       </c>
@@ -25306,9 +24181,6 @@
       </c>
       <c r="H189" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I189" t="str">
-        <v/>
       </c>
     </row>
     <row r="190">
@@ -25321,9 +24193,6 @@
       <c r="C190" t="str">
         <v>JE (EB)</v>
       </c>
-      <c r="D190" t="str">
-        <v/>
-      </c>
       <c r="E190" t="str">
         <v>Gangarani Devi</v>
       </c>
@@ -25335,9 +24204,6 @@
       </c>
       <c r="H190" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I190" t="str">
-        <v/>
       </c>
     </row>
     <row r="191">
@@ -25350,9 +24216,6 @@
       <c r="C191" t="str">
         <v>CGM</v>
       </c>
-      <c r="D191" t="str">
-        <v/>
-      </c>
       <c r="E191" t="str">
         <v>JAI KUMAR SAH</v>
       </c>
@@ -25364,9 +24227,6 @@
       </c>
       <c r="H191" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I191" t="str">
-        <v/>
       </c>
     </row>
     <row r="192">
@@ -25379,9 +24239,6 @@
       <c r="C192" t="str">
         <v>PGM</v>
       </c>
-      <c r="D192" t="str">
-        <v/>
-      </c>
       <c r="E192" t="str">
         <v>M.W.KAZMI</v>
       </c>
@@ -25393,9 +24250,6 @@
       </c>
       <c r="H192" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I192" t="str">
-        <v/>
       </c>
     </row>
     <row r="193">
@@ -25408,9 +24262,6 @@
       <c r="C193" t="str">
         <v>DGM LA</v>
       </c>
-      <c r="D193" t="str">
-        <v/>
-      </c>
       <c r="E193" t="str">
         <v>RAJDEEP</v>
       </c>
@@ -25422,9 +24273,6 @@
       </c>
       <c r="H193" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I193" t="str">
-        <v/>
       </c>
     </row>
     <row r="194">
@@ -25437,9 +24285,6 @@
       <c r="C194" t="str">
         <v>SDE (EB)</v>
       </c>
-      <c r="D194" t="str">
-        <v/>
-      </c>
       <c r="E194" t="str">
         <v>MONIKA SURI</v>
       </c>
@@ -25451,9 +24296,6 @@
       </c>
       <c r="H194" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I194" t="str">
-        <v/>
       </c>
     </row>
     <row r="195">
@@ -25466,9 +24308,6 @@
       <c r="C195" t="str">
         <v>JTO(CRM)</v>
       </c>
-      <c r="D195" t="str">
-        <v/>
-      </c>
       <c r="E195" t="str">
         <v>VIKASH SAINI</v>
       </c>
@@ -25480,9 +24319,6 @@
       </c>
       <c r="H195" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I195" t="str">
-        <v/>
       </c>
     </row>
     <row r="196">
@@ -25495,9 +24331,6 @@
       <c r="C196" t="str">
         <v>JTO(CRM)</v>
       </c>
-      <c r="D196" t="str">
-        <v/>
-      </c>
       <c r="E196" t="str">
         <v>Twinkle Nigam</v>
       </c>
@@ -25509,9 +24342,6 @@
       </c>
       <c r="H196" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I196" t="str">
-        <v/>
       </c>
     </row>
     <row r="197">
@@ -25524,9 +24354,6 @@
       <c r="C197" t="str">
         <v>JTO (CRM)</v>
       </c>
-      <c r="D197" t="str">
-        <v/>
-      </c>
       <c r="E197" t="str">
         <v>ISMAT ZAHRA</v>
       </c>
@@ -25538,9 +24365,6 @@
       </c>
       <c r="H197" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I197" t="str">
-        <v/>
       </c>
     </row>
     <row r="198">
@@ -25553,9 +24377,6 @@
       <c r="C198" t="str">
         <v>SDE(COML)</v>
       </c>
-      <c r="D198" t="str">
-        <v/>
-      </c>
       <c r="E198" t="str">
         <v>GAURAV WAGHELA</v>
       </c>
@@ -25567,9 +24388,6 @@
       </c>
       <c r="H198" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I198" t="str">
-        <v/>
       </c>
     </row>
     <row r="199">
@@ -25582,9 +24400,6 @@
       <c r="C199" t="str">
         <v>JTO (CRM)</v>
       </c>
-      <c r="D199" t="str">
-        <v/>
-      </c>
       <c r="E199" t="str">
         <v>DEEPMALA KOTHARI</v>
       </c>
@@ -25596,9 +24411,6 @@
       </c>
       <c r="H199" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I199" t="str">
-        <v/>
       </c>
     </row>
     <row r="200">
@@ -25611,9 +24423,6 @@
       <c r="C200" t="str">
         <v>SDE (CRM)</v>
       </c>
-      <c r="D200" t="str">
-        <v/>
-      </c>
       <c r="E200" t="str">
         <v>RAKESH KUMAR GUPTA</v>
       </c>
@@ -25625,9 +24434,6 @@
       </c>
       <c r="H200" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I200" t="str">
-        <v/>
       </c>
     </row>
     <row r="201">
@@ -25640,9 +24446,6 @@
       <c r="C201" t="str">
         <v>AGM(BD)</v>
       </c>
-      <c r="D201" t="str">
-        <v/>
-      </c>
       <c r="E201" t="str">
         <v>JUTIKA GOSWAMI SHARMA</v>
       </c>
@@ -25654,9 +24457,6 @@
       </c>
       <c r="H201" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I201" t="str">
-        <v/>
       </c>
     </row>
     <row r="202">
@@ -25669,9 +24469,6 @@
       <c r="C202" t="str">
         <v>SDE(EB-Sales)NAM</v>
       </c>
-      <c r="D202" t="str">
-        <v/>
-      </c>
       <c r="E202" t="str">
         <v>PRITPAL SINGH</v>
       </c>
@@ -25683,9 +24480,6 @@
       </c>
       <c r="H202" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I202" t="str">
-        <v/>
       </c>
     </row>
     <row r="203">
@@ -25698,9 +24492,6 @@
       <c r="C203" t="str">
         <v>SDE</v>
       </c>
-      <c r="D203" t="str">
-        <v/>
-      </c>
       <c r="E203" t="str">
         <v>ANJU PANDEY</v>
       </c>
@@ -25712,9 +24503,6 @@
       </c>
       <c r="H203" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I203" t="str">
-        <v/>
       </c>
     </row>
     <row r="204">
@@ -25727,9 +24515,6 @@
       <c r="C204" t="str">
         <v>SDE (BD)/NAM</v>
       </c>
-      <c r="D204" t="str">
-        <v/>
-      </c>
       <c r="E204" t="str">
         <v>SACHIN KUMAR</v>
       </c>
@@ -25741,9 +24526,6 @@
       </c>
       <c r="H204" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I204" t="str">
-        <v/>
       </c>
     </row>
     <row r="205">
@@ -25756,9 +24538,6 @@
       <c r="C205" t="str">
         <v>SDE(BD)/NAM</v>
       </c>
-      <c r="D205" t="str">
-        <v/>
-      </c>
       <c r="E205" t="str">
         <v>KAMAL SINGH CHAUHAN</v>
       </c>
@@ -25770,9 +24549,6 @@
       </c>
       <c r="H205" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I205" t="str">
-        <v/>
       </c>
     </row>
     <row r="206">
@@ -25785,9 +24561,6 @@
       <c r="C206" t="str">
         <v>JTO (BD)/NAM</v>
       </c>
-      <c r="D206" t="str">
-        <v/>
-      </c>
       <c r="E206" t="str">
         <v>AKANKSHA BHADORIA</v>
       </c>
@@ -25799,9 +24572,6 @@
       </c>
       <c r="H206" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I206" t="str">
-        <v/>
       </c>
     </row>
     <row r="207">
@@ -25814,9 +24584,6 @@
       <c r="C207" t="str">
         <v>JTO NAM &amp; CRM</v>
       </c>
-      <c r="D207" t="str">
-        <v/>
-      </c>
       <c r="E207" t="str">
         <v>SHWETA SHARMA</v>
       </c>
@@ -25828,9 +24595,6 @@
       </c>
       <c r="H207" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I207" t="str">
-        <v/>
       </c>
     </row>
     <row r="208">
@@ -25843,9 +24607,6 @@
       <c r="C208" t="str">
         <v>AGM(CR)</v>
       </c>
-      <c r="D208" t="str">
-        <v/>
-      </c>
       <c r="E208" t="str">
         <v>Suvarchala KH</v>
       </c>
@@ -25857,9 +24618,6 @@
       </c>
       <c r="H208" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I208" t="str">
-        <v/>
       </c>
     </row>
     <row r="209">
@@ -25872,9 +24630,6 @@
       <c r="C209" t="str">
         <v>SDE (COML)</v>
       </c>
-      <c r="D209" t="str">
-        <v/>
-      </c>
       <c r="E209" t="str">
         <v>SHASHI BALA</v>
       </c>
@@ -25886,9 +24641,6 @@
       </c>
       <c r="H209" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I209" t="str">
-        <v/>
       </c>
     </row>
     <row r="210">
@@ -25901,9 +24653,6 @@
       <c r="C210" t="str">
         <v>SDE (BD)/NAM</v>
       </c>
-      <c r="D210" t="str">
-        <v/>
-      </c>
       <c r="E210" t="str">
         <v>DEEPTI GUPTA</v>
       </c>
@@ -25915,9 +24664,6 @@
       </c>
       <c r="H210" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I210" t="str">
-        <v/>
       </c>
     </row>
     <row r="211">
@@ -25930,9 +24676,6 @@
       <c r="C211" t="str">
         <v>JTO COMML</v>
       </c>
-      <c r="D211" t="str">
-        <v/>
-      </c>
       <c r="E211" t="str">
         <v>RACHNA RANI</v>
       </c>
@@ -25944,9 +24687,6 @@
       </c>
       <c r="H211" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I211" t="str">
-        <v/>
       </c>
     </row>
     <row r="212">
@@ -25959,9 +24699,6 @@
       <c r="C212" t="str">
         <v>SDE(EB-1)</v>
       </c>
-      <c r="D212" t="str">
-        <v/>
-      </c>
       <c r="E212" t="str">
         <v>BINOD KUMAR SAH</v>
       </c>
@@ -25973,9 +24710,6 @@
       </c>
       <c r="H212" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I212" t="str">
-        <v/>
       </c>
     </row>
     <row r="213">
@@ -25988,9 +24722,6 @@
       <c r="C213" t="str">
         <v>JTO (COML)</v>
       </c>
-      <c r="D213" t="str">
-        <v/>
-      </c>
       <c r="E213" t="str">
         <v>SHWETA SHARMA</v>
       </c>
@@ -26002,9 +24733,6 @@
       </c>
       <c r="H213" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I213" t="str">
-        <v/>
       </c>
     </row>
     <row r="214">
@@ -26017,9 +24745,6 @@
       <c r="C214" t="str">
         <v>JTO (CRM)</v>
       </c>
-      <c r="D214" t="str">
-        <v/>
-      </c>
       <c r="E214" t="str">
         <v>HIMANSHU KUMAR MEENA</v>
       </c>
@@ -26031,9 +24756,6 @@
       </c>
       <c r="H214" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I214" t="str">
-        <v/>
       </c>
     </row>
     <row r="215">
@@ -26046,9 +24768,6 @@
       <c r="C215" t="str">
         <v>JTO (BD)/ NAM</v>
       </c>
-      <c r="D215" t="str">
-        <v/>
-      </c>
       <c r="E215" t="str">
         <v>DEEPAK SHARMA</v>
       </c>
@@ -26060,9 +24779,6 @@
       </c>
       <c r="H215" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I215" t="str">
-        <v/>
       </c>
     </row>
     <row r="216">
@@ -26075,9 +24791,6 @@
       <c r="C216" t="str">
         <v>JTO(EB-1)</v>
       </c>
-      <c r="D216" t="str">
-        <v/>
-      </c>
       <c r="E216" t="str">
         <v>VISHAL VATS</v>
       </c>
@@ -26089,9 +24802,6 @@
       </c>
       <c r="H216" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I216" t="str">
-        <v/>
       </c>
     </row>
     <row r="217">
@@ -26104,9 +24814,6 @@
       <c r="C217" t="str">
         <v>JE</v>
       </c>
-      <c r="D217" t="str">
-        <v/>
-      </c>
       <c r="E217" t="str">
         <v>PAWAN KUMAR</v>
       </c>
@@ -26118,9 +24825,6 @@
       </c>
       <c r="H217" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I217" t="str">
-        <v/>
       </c>
     </row>
     <row r="218">
@@ -26133,9 +24837,6 @@
       <c r="C218" t="str">
         <v>JE</v>
       </c>
-      <c r="D218" t="str">
-        <v/>
-      </c>
       <c r="E218" t="str">
         <v>SONAM</v>
       </c>
@@ -26147,9 +24848,6 @@
       </c>
       <c r="H218" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I218" t="str">
-        <v/>
       </c>
     </row>
     <row r="219">
@@ -26162,9 +24860,6 @@
       <c r="C219" t="str">
         <v>JE</v>
       </c>
-      <c r="D219" t="str">
-        <v/>
-      </c>
       <c r="E219" t="str">
         <v>MUKTA</v>
       </c>
@@ -26176,9 +24871,6 @@
       </c>
       <c r="H219" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I219" t="str">
-        <v/>
       </c>
     </row>
     <row r="220">
@@ -26191,9 +24883,6 @@
       <c r="C220" t="str">
         <v>JE</v>
       </c>
-      <c r="D220" t="str">
-        <v/>
-      </c>
       <c r="E220" t="str">
         <v>BIPIN SINGH</v>
       </c>
@@ -26205,9 +24894,6 @@
       </c>
       <c r="H220" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I220" t="str">
-        <v/>
       </c>
     </row>
     <row r="221">
@@ -26220,9 +24906,6 @@
       <c r="C221" t="str">
         <v>DRIVER</v>
       </c>
-      <c r="D221" t="str">
-        <v/>
-      </c>
       <c r="E221" t="str">
         <v>DINESH</v>
       </c>
@@ -26234,9 +24917,6 @@
       </c>
       <c r="H221" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I221" t="str">
-        <v/>
       </c>
     </row>
     <row r="222">
@@ -26249,9 +24929,6 @@
       <c r="C222" t="str">
         <v>ATT</v>
       </c>
-      <c r="D222" t="str">
-        <v/>
-      </c>
       <c r="E222" t="str">
         <v>YOGESH KUMAR</v>
       </c>
@@ -26263,9 +24940,6 @@
       </c>
       <c r="H222" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I222" t="str">
-        <v/>
       </c>
     </row>
     <row r="223">
@@ -26278,9 +24952,6 @@
       <c r="C223" t="str">
         <v>ATT</v>
       </c>
-      <c r="D223" t="str">
-        <v/>
-      </c>
       <c r="E223" t="str">
         <v>SANTER PAL</v>
       </c>
@@ -26292,9 +24963,6 @@
       </c>
       <c r="H223" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I223" t="str">
-        <v/>
       </c>
     </row>
     <row r="224">
@@ -26307,9 +24975,6 @@
       <c r="C224" t="str">
         <v>ATT</v>
       </c>
-      <c r="D224" t="str">
-        <v/>
-      </c>
       <c r="E224" t="str">
         <v>MUNNI DEVI</v>
       </c>
@@ -26321,9 +24986,6 @@
       </c>
       <c r="H224" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I224" t="str">
-        <v/>
       </c>
     </row>
     <row r="225">
@@ -26336,9 +24998,6 @@
       <c r="C225" t="str">
         <v>CGM</v>
       </c>
-      <c r="D225" t="str">
-        <v/>
-      </c>
       <c r="E225" t="str">
         <v>JAI KUMAR SAH</v>
       </c>
@@ -26350,9 +25009,6 @@
       </c>
       <c r="H225" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I225" t="str">
-        <v/>
       </c>
     </row>
     <row r="226">
@@ -26365,9 +25021,6 @@
       <c r="C226" t="str">
         <v>Sr.GM (EB NCR-II)</v>
       </c>
-      <c r="D226" t="str">
-        <v/>
-      </c>
       <c r="E226" t="str">
         <v>Sudhir Kumar Mishra</v>
       </c>
@@ -26379,9 +25032,6 @@
       </c>
       <c r="H226" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I226" t="str">
-        <v/>
       </c>
     </row>
     <row r="227">
@@ -26394,9 +25044,6 @@
       <c r="C227" t="str">
         <v>DGM(EB-II) L/A</v>
       </c>
-      <c r="D227" t="str">
-        <v/>
-      </c>
       <c r="E227" t="str">
         <v>Deepika Mirani</v>
       </c>
@@ -26408,9 +25055,6 @@
       </c>
       <c r="H227" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I227" t="str">
-        <v/>
       </c>
     </row>
     <row r="228">
@@ -26423,9 +25067,6 @@
       <c r="C228" t="str">
         <v>DGM(EB-project)</v>
       </c>
-      <c r="D228" t="str">
-        <v/>
-      </c>
       <c r="E228" t="str">
         <v>Chandrabhan Yadav</v>
       </c>
@@ -26437,9 +25078,6 @@
       </c>
       <c r="H228" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I228" t="str">
-        <v/>
       </c>
     </row>
     <row r="229">
@@ -26452,9 +25090,6 @@
       <c r="C229" t="str">
         <v>AGM</v>
       </c>
-      <c r="D229" t="str">
-        <v/>
-      </c>
       <c r="E229" t="str">
         <v>Anita Singh</v>
       </c>
@@ -26466,9 +25101,6 @@
       </c>
       <c r="H229" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I229" t="str">
-        <v/>
       </c>
     </row>
     <row r="230">
@@ -26481,9 +25113,6 @@
       <c r="C230" t="str">
         <v>AGM(EB-Project)</v>
       </c>
-      <c r="D230" t="str">
-        <v/>
-      </c>
       <c r="E230" t="str">
         <v>Devendra Pal Singh</v>
       </c>
@@ -26495,9 +25124,6 @@
       </c>
       <c r="H230" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I230" t="str">
-        <v/>
       </c>
     </row>
     <row r="231">
@@ -26510,9 +25136,6 @@
       <c r="C231" t="str">
         <v>AGM Legal/CRM</v>
       </c>
-      <c r="D231" t="str">
-        <v/>
-      </c>
       <c r="E231" t="str">
         <v>Salim</v>
       </c>
@@ -26524,9 +25147,6 @@
       </c>
       <c r="H231" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I231" t="str">
-        <v/>
       </c>
     </row>
     <row r="232">
@@ -26539,9 +25159,6 @@
       <c r="C232" t="str">
         <v>SDE</v>
       </c>
-      <c r="D232" t="str">
-        <v/>
-      </c>
       <c r="E232" t="str">
         <v>Umesh Chaddha</v>
       </c>
@@ -26553,9 +25170,6 @@
       </c>
       <c r="H232" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I232" t="str">
-        <v/>
       </c>
     </row>
     <row r="233">
@@ -26568,9 +25182,6 @@
       <c r="C233" t="str">
         <v>SDE</v>
       </c>
-      <c r="D233" t="str">
-        <v/>
-      </c>
       <c r="E233" t="str">
         <v>Davinder Singh</v>
       </c>
@@ -26582,9 +25193,6 @@
       </c>
       <c r="H233" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I233" t="str">
-        <v/>
       </c>
     </row>
     <row r="234">
@@ -26597,9 +25205,6 @@
       <c r="C234" t="str">
         <v>AD(O/L)/ SDE</v>
       </c>
-      <c r="D234" t="str">
-        <v/>
-      </c>
       <c r="E234" t="str">
         <v>Kamini Singh</v>
       </c>
@@ -26611,9 +25216,6 @@
       </c>
       <c r="H234" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I234" t="str">
-        <v/>
       </c>
     </row>
     <row r="235">
@@ -26626,9 +25228,6 @@
       <c r="C235" t="str">
         <v>SDE</v>
       </c>
-      <c r="D235" t="str">
-        <v/>
-      </c>
       <c r="E235" t="str">
         <v>Kamal Kishor Meena</v>
       </c>
@@ -26640,9 +25239,6 @@
       </c>
       <c r="H235" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I235" t="str">
-        <v/>
       </c>
     </row>
     <row r="236">
@@ -26655,9 +25251,6 @@
       <c r="C236" t="str">
         <v>SDE</v>
       </c>
-      <c r="D236" t="str">
-        <v/>
-      </c>
       <c r="E236" t="str">
         <v>Rajat Kapoor</v>
       </c>
@@ -26669,9 +25262,6 @@
       </c>
       <c r="H236" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I236" t="str">
-        <v/>
       </c>
     </row>
     <row r="237">
@@ -26684,9 +25274,6 @@
       <c r="C237" t="str">
         <v>SDE</v>
       </c>
-      <c r="D237" t="str">
-        <v/>
-      </c>
       <c r="E237" t="str">
         <v>Kanika Jindal</v>
       </c>
@@ -26698,9 +25285,6 @@
       </c>
       <c r="H237" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I237" t="str">
-        <v/>
       </c>
     </row>
     <row r="238">
@@ -26713,9 +25297,6 @@
       <c r="C238" t="str">
         <v>SDE</v>
       </c>
-      <c r="D238" t="str">
-        <v/>
-      </c>
       <c r="E238" t="str">
         <v>Achal Rastogi</v>
       </c>
@@ -26727,9 +25308,6 @@
       </c>
       <c r="H238" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I238" t="str">
-        <v/>
       </c>
     </row>
     <row r="239">
@@ -26742,9 +25320,6 @@
       <c r="C239" t="str">
         <v>SDE</v>
       </c>
-      <c r="D239" t="str">
-        <v/>
-      </c>
       <c r="E239" t="str">
         <v>Vinay Kumar</v>
       </c>
@@ -26756,9 +25331,6 @@
       </c>
       <c r="H239" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I239" t="str">
-        <v/>
       </c>
     </row>
     <row r="240">
@@ -26771,9 +25343,6 @@
       <c r="C240" t="str">
         <v>SDE</v>
       </c>
-      <c r="D240" t="str">
-        <v/>
-      </c>
       <c r="E240" t="str">
         <v>Bhupendra Singh</v>
       </c>
@@ -26785,9 +25354,6 @@
       </c>
       <c r="H240" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I240" t="str">
-        <v/>
       </c>
     </row>
     <row r="241">
@@ -26800,9 +25366,6 @@
       <c r="C241" t="str">
         <v>JTO</v>
       </c>
-      <c r="D241" t="str">
-        <v/>
-      </c>
       <c r="E241" t="str">
         <v>Nitika Saini</v>
       </c>
@@ -26814,9 +25377,6 @@
       </c>
       <c r="H241" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I241" t="str">
-        <v/>
       </c>
     </row>
     <row r="242">
@@ -26829,9 +25389,6 @@
       <c r="C242" t="str">
         <v>JTO</v>
       </c>
-      <c r="D242" t="str">
-        <v/>
-      </c>
       <c r="E242" t="str">
         <v>Sonam Dogra</v>
       </c>
@@ -26843,9 +25400,6 @@
       </c>
       <c r="H242" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I242" t="str">
-        <v/>
       </c>
     </row>
     <row r="243">
@@ -26858,9 +25412,6 @@
       <c r="C243" t="str">
         <v>JTO</v>
       </c>
-      <c r="D243" t="str">
-        <v/>
-      </c>
       <c r="E243" t="str">
         <v>Karanvir Singh</v>
       </c>
@@ -26872,9 +25423,6 @@
       </c>
       <c r="H243" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I243" t="str">
-        <v/>
       </c>
     </row>
     <row r="244">
@@ -26887,9 +25435,6 @@
       <c r="C244" t="str">
         <v>JTO</v>
       </c>
-      <c r="D244" t="str">
-        <v/>
-      </c>
       <c r="E244" t="str">
         <v>Sanjay Kumar</v>
       </c>
@@ -26901,9 +25446,6 @@
       </c>
       <c r="H244" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I244" t="str">
-        <v/>
       </c>
     </row>
     <row r="245">
@@ -26916,9 +25458,6 @@
       <c r="C245" t="str">
         <v>JTO</v>
       </c>
-      <c r="D245" t="str">
-        <v/>
-      </c>
       <c r="E245" t="str">
         <v>Gaurav Tewatia</v>
       </c>
@@ -26930,9 +25469,6 @@
       </c>
       <c r="H245" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I245" t="str">
-        <v/>
       </c>
     </row>
     <row r="246">
@@ -26945,9 +25481,6 @@
       <c r="C246" t="str">
         <v>JTO</v>
       </c>
-      <c r="D246" t="str">
-        <v/>
-      </c>
       <c r="E246" t="str">
         <v>Saini</v>
       </c>
@@ -26959,9 +25492,6 @@
       </c>
       <c r="H246" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I246" t="str">
-        <v/>
       </c>
     </row>
     <row r="247">
@@ -26974,9 +25504,6 @@
       <c r="C247" t="str">
         <v>JE</v>
       </c>
-      <c r="D247" t="str">
-        <v/>
-      </c>
       <c r="E247" t="str">
         <v>Sumit Kumar</v>
       </c>
@@ -26988,9 +25515,6 @@
       </c>
       <c r="H247" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I247" t="str">
-        <v/>
       </c>
     </row>
     <row r="248">
@@ -27003,9 +25527,6 @@
       <c r="C248" t="str">
         <v>GM</v>
       </c>
-      <c r="D248" t="str">
-        <v/>
-      </c>
       <c r="E248" t="str">
         <v>Sh.Yogesh Kumar Maurya</v>
       </c>
@@ -27017,9 +25538,6 @@
       </c>
       <c r="H248" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I248" t="str">
-        <v/>
       </c>
     </row>
     <row r="249">
@@ -27032,9 +25550,6 @@
       <c r="C249" t="str">
         <v>DGM</v>
       </c>
-      <c r="D249" t="str">
-        <v/>
-      </c>
       <c r="E249" t="str">
         <v>Sh.Shivprasad Shankarlal Rajoriya</v>
       </c>
@@ -27046,9 +25561,6 @@
       </c>
       <c r="H249" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I249" t="str">
-        <v/>
       </c>
     </row>
     <row r="250">
@@ -27061,9 +25573,6 @@
       <c r="C250" t="str">
         <v>DE (LC)</v>
       </c>
-      <c r="D250" t="str">
-        <v/>
-      </c>
       <c r="E250" t="str">
         <v>Sh.Tashi Gyalstan</v>
       </c>
@@ -27075,9 +25584,6 @@
       </c>
       <c r="H250" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I250" t="str">
-        <v/>
       </c>
     </row>
     <row r="251">
@@ -27090,9 +25596,6 @@
       <c r="C251" t="str">
         <v>JTO (LC)</v>
       </c>
-      <c r="D251" t="str">
-        <v/>
-      </c>
       <c r="E251" t="str">
         <v>Sh.Hemant Kumar</v>
       </c>
@@ -27104,9 +25607,6 @@
       </c>
       <c r="H251" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I251" t="str">
-        <v/>
       </c>
     </row>
     <row r="252">
@@ -27119,9 +25619,6 @@
       <c r="C252" t="str">
         <v>CGM</v>
       </c>
-      <c r="D252" t="str">
-        <v/>
-      </c>
       <c r="E252" t="str">
         <v>Sri D.K.Behera</v>
       </c>
@@ -27133,9 +25630,6 @@
       </c>
       <c r="H252" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I252" t="str">
-        <v/>
       </c>
     </row>
     <row r="253">
@@ -27148,9 +25642,6 @@
       <c r="C253" t="str">
         <v>DGM (EB-CRM)</v>
       </c>
-      <c r="D253" t="str">
-        <v/>
-      </c>
       <c r="E253" t="str">
         <v>Sri Naba Kishore Sahoo</v>
       </c>
@@ -27162,9 +25653,6 @@
       </c>
       <c r="H253" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I253" t="str">
-        <v/>
       </c>
     </row>
     <row r="254">
@@ -27177,9 +25665,6 @@
       <c r="C254" t="str">
         <v>AGM (EB-CRM)</v>
       </c>
-      <c r="D254" t="str">
-        <v/>
-      </c>
       <c r="E254" t="str">
         <v>Sri Shiva Kumar Sahu</v>
       </c>
@@ -27191,9 +25676,6 @@
       </c>
       <c r="H254" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I254" t="str">
-        <v/>
       </c>
     </row>
     <row r="255">
@@ -27206,9 +25688,6 @@
       <c r="C255" t="str">
         <v>AGM (EB-NB)</v>
       </c>
-      <c r="D255" t="str">
-        <v/>
-      </c>
       <c r="E255" t="str">
         <v>Sri Santosh Kumar Behera</v>
       </c>
@@ -27220,9 +25699,6 @@
       </c>
       <c r="H255" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I255" t="str">
-        <v/>
       </c>
     </row>
     <row r="256">
@@ -27235,9 +25711,6 @@
       <c r="C256" t="str">
         <v>SDE (EB-NB-II)</v>
       </c>
-      <c r="D256" t="str">
-        <v/>
-      </c>
       <c r="E256" t="str">
         <v>Sri Deepak Kumar Sahoo</v>
       </c>
@@ -27249,9 +25722,6 @@
       </c>
       <c r="H256" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I256" t="str">
-        <v/>
       </c>
     </row>
     <row r="257">
@@ -27264,9 +25734,6 @@
       <c r="C257" t="str">
         <v>SDE (EB-CRM-I)</v>
       </c>
-      <c r="D257" t="str">
-        <v/>
-      </c>
       <c r="E257" t="str">
         <v>Sri Samir Kumar Dhal</v>
       </c>
@@ -27278,9 +25745,6 @@
       </c>
       <c r="H257" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I257" t="str">
-        <v/>
       </c>
     </row>
     <row r="258">
@@ -27293,9 +25757,6 @@
       <c r="C258" t="str">
         <v>JTO (EB-CRM-I)</v>
       </c>
-      <c r="D258" t="str">
-        <v/>
-      </c>
       <c r="E258" t="str">
         <v>Sri Banabihari Narendra Singh</v>
       </c>
@@ -27307,9 +25768,6 @@
       </c>
       <c r="H258" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I258" t="str">
-        <v/>
       </c>
     </row>
     <row r="259">
@@ -27322,9 +25780,6 @@
       <c r="C259" t="str">
         <v>SDE (EB-CRM-II</v>
       </c>
-      <c r="D259" t="str">
-        <v/>
-      </c>
       <c r="E259" t="str">
         <v>Santosh kumar Badapanda</v>
       </c>
@@ -27336,9 +25791,6 @@
       </c>
       <c r="H259" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I259" t="str">
-        <v/>
       </c>
     </row>
     <row r="260">
@@ -27351,9 +25803,6 @@
       <c r="C260" t="str">
         <v>SDE (EB-CRM-III)</v>
       </c>
-      <c r="D260" t="str">
-        <v/>
-      </c>
       <c r="E260" t="str">
         <v>Chita Ranjan Sahoo</v>
       </c>
@@ -27365,9 +25814,6 @@
       </c>
       <c r="H260" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I260" t="str">
-        <v/>
       </c>
     </row>
     <row r="261">
@@ -27380,9 +25826,6 @@
       <c r="C261" t="str">
         <v>JTO (EB NB)</v>
       </c>
-      <c r="D261" t="str">
-        <v/>
-      </c>
       <c r="E261" t="str">
         <v>Sri D N Senapaty</v>
       </c>
@@ -27394,9 +25837,6 @@
       </c>
       <c r="H261" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I261" t="str">
-        <v/>
       </c>
     </row>
     <row r="262">
@@ -27409,9 +25849,6 @@
       <c r="C262" t="str">
         <v>JTO(DOPNW)</v>
       </c>
-      <c r="D262" t="str">
-        <v/>
-      </c>
       <c r="E262" t="str">
         <v>TARUN PRAKASH SETHI</v>
       </c>
@@ -27423,9 +25860,6 @@
       </c>
       <c r="H262" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I262" t="str">
-        <v/>
       </c>
     </row>
     <row r="263">
@@ -27438,9 +25872,6 @@
       <c r="C263" t="str">
         <v>CGM</v>
       </c>
-      <c r="D263" t="str">
-        <v/>
-      </c>
       <c r="E263" t="str">
         <v>Ajay Kararha</v>
       </c>
@@ -27452,9 +25883,6 @@
       </c>
       <c r="H263" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I263" t="str">
-        <v/>
       </c>
     </row>
     <row r="264">
@@ -27467,9 +25895,6 @@
       <c r="C264" t="str">
         <v>GM (EB)</v>
       </c>
-      <c r="D264" t="str">
-        <v/>
-      </c>
       <c r="E264" t="str">
         <v>S.C.Badal</v>
       </c>
@@ -27481,9 +25906,6 @@
       </c>
       <c r="H264" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I264" t="str">
-        <v/>
       </c>
     </row>
     <row r="265">
@@ -27496,9 +25918,6 @@
       <c r="C265" t="str">
         <v>DGM (EB)</v>
       </c>
-      <c r="D265" t="str">
-        <v/>
-      </c>
       <c r="E265" t="str">
         <v>Munish Kapoor</v>
       </c>
@@ -27510,9 +25929,6 @@
       </c>
       <c r="H265" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I265" t="str">
-        <v/>
       </c>
     </row>
     <row r="266">
@@ -27525,9 +25941,6 @@
       <c r="C266" t="str">
         <v>AGM (LC)</v>
       </c>
-      <c r="D266" t="str">
-        <v/>
-      </c>
       <c r="E266" t="str">
         <v>Randeep Singh Chandel</v>
       </c>
@@ -27539,9 +25952,6 @@
       </c>
       <c r="H266" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I266" t="str">
-        <v/>
       </c>
     </row>
     <row r="267">
@@ -27554,9 +25964,6 @@
       <c r="C267" t="str">
         <v>AD (LC-2)</v>
       </c>
-      <c r="D267" t="str">
-        <v/>
-      </c>
       <c r="E267" t="str">
         <v>Rajni Sehgal</v>
       </c>
@@ -27568,9 +25975,6 @@
       </c>
       <c r="H267" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I267" t="str">
-        <v/>
       </c>
     </row>
     <row r="268">
@@ -27583,9 +25987,6 @@
       <c r="C268" t="str">
         <v>AD (LC-1)</v>
       </c>
-      <c r="D268" t="str">
-        <v/>
-      </c>
       <c r="E268" t="str">
         <v>Vinod</v>
       </c>
@@ -27597,9 +25998,6 @@
       </c>
       <c r="H268" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I268" t="str">
-        <v/>
       </c>
     </row>
     <row r="269">
@@ -27612,9 +26010,6 @@
       <c r="C269" t="str">
         <v>JE(LC)</v>
       </c>
-      <c r="D269" t="str">
-        <v/>
-      </c>
       <c r="E269" t="str">
         <v>Shruti Tandon</v>
       </c>
@@ -27626,9 +26021,6 @@
       </c>
       <c r="H269" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I269" t="str">
-        <v/>
       </c>
     </row>
     <row r="270">
@@ -27641,9 +26033,6 @@
       <c r="C270" t="str">
         <v>AGM (EB)</v>
       </c>
-      <c r="D270" t="str">
-        <v/>
-      </c>
       <c r="E270" t="str">
         <v>Gaurav Singh Aulakh</v>
       </c>
@@ -27655,9 +26044,6 @@
       </c>
       <c r="H270" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I270" t="str">
-        <v/>
       </c>
     </row>
     <row r="271">
@@ -27670,9 +26056,6 @@
       <c r="C271" t="str">
         <v>AD EB-III</v>
       </c>
-      <c r="D271" t="str">
-        <v/>
-      </c>
       <c r="E271" t="str">
         <v>Ranjit singh</v>
       </c>
@@ -27684,9 +26067,6 @@
       </c>
       <c r="H271" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I271" t="str">
-        <v/>
       </c>
     </row>
     <row r="272">
@@ -27699,9 +26079,6 @@
       <c r="C272" t="str">
         <v>AD EB-II</v>
       </c>
-      <c r="D272" t="str">
-        <v/>
-      </c>
       <c r="E272" t="str">
         <v>Gaurav Pathak</v>
       </c>
@@ -27713,9 +26090,6 @@
       </c>
       <c r="H272" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I272" t="str">
-        <v/>
       </c>
     </row>
     <row r="273">
@@ -27728,9 +26102,6 @@
       <c r="C273" t="str">
         <v>AD CRM</v>
       </c>
-      <c r="D273" t="str">
-        <v/>
-      </c>
       <c r="E273" t="str">
         <v>Sandeep Sachan</v>
       </c>
@@ -27742,9 +26113,6 @@
       </c>
       <c r="H273" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I273" t="str">
-        <v/>
       </c>
     </row>
     <row r="274">
@@ -27757,9 +26125,6 @@
       <c r="C274" t="str">
         <v>AD CRM-III (EB)</v>
       </c>
-      <c r="D274" t="str">
-        <v/>
-      </c>
       <c r="E274" t="str">
         <v>Pardeep Hetta</v>
       </c>
@@ -27771,9 +26136,6 @@
       </c>
       <c r="H274" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I274" t="str">
-        <v/>
       </c>
     </row>
     <row r="275">
@@ -27786,9 +26148,6 @@
       <c r="C275" t="str">
         <v>CGM</v>
       </c>
-      <c r="D275" t="str">
-        <v/>
-      </c>
       <c r="E275" t="str">
         <v>Sh. Vikram Malviya Ji</v>
       </c>
@@ -27800,9 +26159,6 @@
       </c>
       <c r="H275" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I275" t="str">
-        <v/>
       </c>
     </row>
     <row r="276">
@@ -27815,9 +26171,6 @@
       <c r="C276" t="str">
         <v>PGM</v>
       </c>
-      <c r="D276" t="str">
-        <v/>
-      </c>
       <c r="E276" t="str">
         <v>SUBHASH CHANDER AGARWAL</v>
       </c>
@@ -27829,9 +26182,6 @@
       </c>
       <c r="H276" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I276" t="str">
-        <v/>
       </c>
     </row>
     <row r="277">
@@ -27844,9 +26194,6 @@
       <c r="C277" t="str">
         <v>DGM</v>
       </c>
-      <c r="D277" t="str">
-        <v/>
-      </c>
       <c r="E277" t="str">
         <v>Hari Kishan Tambia</v>
       </c>
@@ -27858,9 +26205,6 @@
       </c>
       <c r="H277" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I277" t="str">
-        <v/>
       </c>
     </row>
     <row r="278">
@@ -27873,9 +26217,6 @@
       <c r="C278" t="str">
         <v>AGM</v>
       </c>
-      <c r="D278" t="str">
-        <v/>
-      </c>
       <c r="E278" t="str">
         <v>KK Kumawat</v>
       </c>
@@ -27887,9 +26228,6 @@
       </c>
       <c r="H278" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I278" t="str">
-        <v/>
       </c>
     </row>
     <row r="279">
@@ -27902,9 +26240,6 @@
       <c r="C279" t="str">
         <v>AD</v>
       </c>
-      <c r="D279" t="str">
-        <v/>
-      </c>
       <c r="E279" t="str">
         <v>Praveen Bhatt</v>
       </c>
@@ -27916,9 +26251,6 @@
       </c>
       <c r="H279" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I279" t="str">
-        <v/>
       </c>
     </row>
     <row r="280">
@@ -27931,9 +26263,6 @@
       <c r="C280" t="str">
         <v>AD</v>
       </c>
-      <c r="D280" t="str">
-        <v/>
-      </c>
       <c r="E280" t="str">
         <v>Dushyant Sharma</v>
       </c>
@@ -27945,9 +26274,6 @@
       </c>
       <c r="H280" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I280" t="str">
-        <v/>
       </c>
     </row>
     <row r="281">
@@ -27960,9 +26286,6 @@
       <c r="C281" t="str">
         <v>AD</v>
       </c>
-      <c r="D281" t="str">
-        <v/>
-      </c>
       <c r="E281" t="str">
         <v>Udai Singh Meena</v>
       </c>
@@ -27974,9 +26297,6 @@
       </c>
       <c r="H281" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I281" t="str">
-        <v/>
       </c>
     </row>
     <row r="282">
@@ -27989,9 +26309,6 @@
       <c r="C282" t="str">
         <v>AD</v>
       </c>
-      <c r="D282" t="str">
-        <v/>
-      </c>
       <c r="E282" t="str">
         <v>Neeraj Gautam</v>
       </c>
@@ -28003,9 +26320,6 @@
       </c>
       <c r="H282" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I282" t="str">
-        <v/>
       </c>
     </row>
     <row r="283">
@@ -28018,9 +26332,6 @@
       <c r="C283" t="str">
         <v>AD</v>
       </c>
-      <c r="D283" t="str">
-        <v/>
-      </c>
       <c r="E283" t="str">
         <v>Monika Minocha</v>
       </c>
@@ -28032,9 +26343,6 @@
       </c>
       <c r="H283" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I283" t="str">
-        <v/>
       </c>
     </row>
     <row r="284">
@@ -28047,9 +26355,6 @@
       <c r="C284" t="str">
         <v>AD</v>
       </c>
-      <c r="D284" t="str">
-        <v/>
-      </c>
       <c r="E284" t="str">
         <v>Ravi Mehta</v>
       </c>
@@ -28061,9 +26366,6 @@
       </c>
       <c r="H284" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I284" t="str">
-        <v/>
       </c>
     </row>
     <row r="285">
@@ -28076,9 +26378,6 @@
       <c r="C285" t="str">
         <v>AD</v>
       </c>
-      <c r="D285" t="str">
-        <v/>
-      </c>
       <c r="E285" t="str">
         <v>Shree Ram Meena</v>
       </c>
@@ -28090,9 +26389,6 @@
       </c>
       <c r="H285" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I285" t="str">
-        <v/>
       </c>
     </row>
     <row r="286">
@@ -28105,9 +26401,6 @@
       <c r="C286" t="str">
         <v>JTO</v>
       </c>
-      <c r="D286" t="str">
-        <v/>
-      </c>
       <c r="E286" t="str">
         <v>Ankush Jain</v>
       </c>
@@ -28119,9 +26412,6 @@
       </c>
       <c r="H286" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I286" t="str">
-        <v/>
       </c>
     </row>
     <row r="287">
@@ -28134,9 +26424,6 @@
       <c r="C287" t="str">
         <v>CGM</v>
       </c>
-      <c r="D287" t="str">
-        <v/>
-      </c>
       <c r="E287" t="str">
         <v>M K Yadav</v>
       </c>
@@ -28148,9 +26435,6 @@
       </c>
       <c r="H287" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I287" t="str">
-        <v/>
       </c>
     </row>
     <row r="288">
@@ -28163,9 +26447,6 @@
       <c r="C288" t="str">
         <v>GM</v>
       </c>
-      <c r="D288" t="str">
-        <v/>
-      </c>
       <c r="E288" t="str">
         <v>K K Sinha</v>
       </c>
@@ -28177,9 +26458,6 @@
       </c>
       <c r="H288" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I288" t="str">
-        <v/>
       </c>
     </row>
     <row r="289">
@@ -28192,9 +26470,6 @@
       <c r="C289" t="str">
         <v>DGM</v>
       </c>
-      <c r="D289" t="str">
-        <v/>
-      </c>
       <c r="E289" t="str">
         <v>KAKAD ULHAS BANDU</v>
       </c>
@@ -28206,9 +26481,6 @@
       </c>
       <c r="H289" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I289" t="str">
-        <v/>
       </c>
     </row>
     <row r="290">
@@ -28221,9 +26493,6 @@
       <c r="C290" t="str">
         <v>AGM</v>
       </c>
-      <c r="D290" t="str">
-        <v/>
-      </c>
       <c r="E290" t="str">
         <v>Chaure R K</v>
       </c>
@@ -28235,9 +26504,6 @@
       </c>
       <c r="H290" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I290" t="str">
-        <v/>
       </c>
     </row>
     <row r="291">
@@ -28250,9 +26516,6 @@
       <c r="C291" t="str">
         <v>SDE</v>
       </c>
-      <c r="D291" t="str">
-        <v/>
-      </c>
       <c r="E291" t="str">
         <v>M. BALA KRISHNA</v>
       </c>
@@ -28264,9 +26527,6 @@
       </c>
       <c r="H291" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I291" t="str">
-        <v/>
       </c>
     </row>
     <row r="292">
@@ -28279,9 +26539,6 @@
       <c r="C292" t="str">
         <v>JTO</v>
       </c>
-      <c r="D292" t="str">
-        <v/>
-      </c>
       <c r="E292" t="str">
         <v>TEKENDRA SUBEDI</v>
       </c>
@@ -28293,9 +26550,6 @@
       </c>
       <c r="H292" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I292" t="str">
-        <v/>
       </c>
     </row>
     <row r="293">
@@ -28308,9 +26562,6 @@
       <c r="C293" t="str">
         <v>JTO</v>
       </c>
-      <c r="D293" t="str">
-        <v/>
-      </c>
       <c r="E293" t="str">
         <v>SHAILENDRA LAMA</v>
       </c>
@@ -28322,9 +26573,6 @@
       </c>
       <c r="H293" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I293" t="str">
-        <v/>
       </c>
     </row>
     <row r="294">
@@ -28337,9 +26585,6 @@
       <c r="C294" t="str">
         <v>JE</v>
       </c>
-      <c r="D294" t="str">
-        <v/>
-      </c>
       <c r="E294" t="str">
         <v>RAKESH ROSHAN GURUNG</v>
       </c>
@@ -28351,9 +26596,6 @@
       </c>
       <c r="H294" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I294" t="str">
-        <v/>
       </c>
     </row>
     <row r="295">
@@ -28366,9 +26608,6 @@
       <c r="C295" t="str">
         <v>CGM (MPLS &amp; EB)</v>
       </c>
-      <c r="D295" t="str">
-        <v/>
-      </c>
       <c r="E295" t="str">
         <v>P Murali Mohan</v>
       </c>
@@ -28380,9 +26619,6 @@
       </c>
       <c r="H295" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I295" t="str">
-        <v/>
       </c>
     </row>
     <row r="296">
@@ -28395,9 +26631,6 @@
       <c r="C296" t="str">
         <v>GM (EBP)</v>
       </c>
-      <c r="D296" t="str">
-        <v/>
-      </c>
       <c r="E296" t="str">
         <v>Musa Abhisek</v>
       </c>
@@ -28409,9 +26642,6 @@
       </c>
       <c r="H296" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I296" t="str">
-        <v/>
       </c>
     </row>
     <row r="297">
@@ -28424,9 +26654,6 @@
       <c r="C297" t="str">
         <v>PGM (SAT)</v>
       </c>
-      <c r="D297" t="str">
-        <v/>
-      </c>
       <c r="E297" t="str">
         <v>P. Vinod chandran</v>
       </c>
@@ -28438,9 +26665,6 @@
       </c>
       <c r="H297" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I297" t="str">
-        <v/>
       </c>
     </row>
     <row r="298">
@@ -28453,9 +26677,6 @@
       <c r="C298" t="str">
         <v>DGM (EB &amp; BD)</v>
       </c>
-      <c r="D298" t="str">
-        <v/>
-      </c>
       <c r="E298" t="str">
         <v>Ramakanth Sarma</v>
       </c>
@@ -28467,9 +26688,6 @@
       </c>
       <c r="H298" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I298" t="str">
-        <v/>
       </c>
     </row>
     <row r="299">
@@ -28482,9 +26700,6 @@
       <c r="C299" t="str">
         <v>DE (Hub &amp; FC)</v>
       </c>
-      <c r="D299" t="str">
-        <v/>
-      </c>
       <c r="E299" t="str">
         <v>P. Parijatha Kumar</v>
       </c>
@@ -28496,9 +26711,6 @@
       </c>
       <c r="H299" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I299" t="str">
-        <v/>
       </c>
     </row>
     <row r="300">
@@ -28511,9 +26723,6 @@
       <c r="C300" t="str">
         <v>DE (EBP)</v>
       </c>
-      <c r="D300" t="str">
-        <v/>
-      </c>
       <c r="E300" t="str">
         <v>Ramakanth Sarma</v>
       </c>
@@ -28525,9 +26734,6 @@
       </c>
       <c r="H300" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I300" t="str">
-        <v/>
       </c>
     </row>
     <row r="301">
@@ -28540,9 +26746,6 @@
       <c r="C301" t="str">
         <v>SDE (CRM &amp; Comm)</v>
       </c>
-      <c r="D301" t="str">
-        <v/>
-      </c>
       <c r="E301" t="str">
         <v>M. Narasimhulu</v>
       </c>
@@ -28554,9 +26757,6 @@
       </c>
       <c r="H301" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I301" t="str">
-        <v/>
       </c>
     </row>
     <row r="302">
@@ -28569,9 +26769,6 @@
       <c r="C302" t="str">
         <v>SDE (Plg &amp; stores)</v>
       </c>
-      <c r="D302" t="str">
-        <v/>
-      </c>
       <c r="E302" t="str">
         <v>V. Kumarswamy</v>
       </c>
@@ -28583,9 +26780,6 @@
       </c>
       <c r="H302" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I302" t="str">
-        <v/>
       </c>
     </row>
     <row r="303">
@@ -28598,9 +26792,6 @@
       <c r="C303" t="str">
         <v>CGM</v>
       </c>
-      <c r="D303" t="str">
-        <v/>
-      </c>
       <c r="E303" t="str">
         <v>Shri Parthiban S</v>
       </c>
@@ -28612,9 +26803,6 @@
       </c>
       <c r="H303" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I303" t="str">
-        <v/>
       </c>
     </row>
     <row r="304">
@@ -28627,9 +26815,6 @@
       <c r="C304" t="str">
         <v>PGM (EB)</v>
       </c>
-      <c r="D304" t="str">
-        <v/>
-      </c>
       <c r="E304" t="str">
         <v>Rachana Singh</v>
       </c>
@@ -28641,9 +26826,6 @@
       </c>
       <c r="H304" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I304" t="str">
-        <v/>
       </c>
     </row>
     <row r="305">
@@ -28656,9 +26838,6 @@
       <c r="C305" t="str">
         <v>DGM(Sales)</v>
       </c>
-      <c r="D305" t="str">
-        <v/>
-      </c>
       <c r="E305" t="str">
         <v>Smt. Umamaheswari K J</v>
       </c>
@@ -28670,9 +26849,6 @@
       </c>
       <c r="H305" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I305" t="str">
-        <v/>
       </c>
     </row>
     <row r="306">
@@ -28685,9 +26861,6 @@
       <c r="C306" t="str">
         <v>DGM(SD)</v>
       </c>
-      <c r="D306" t="str">
-        <v/>
-      </c>
       <c r="E306" t="str">
         <v>CHANDRASEKARAN R</v>
       </c>
@@ -28699,9 +26872,6 @@
       </c>
       <c r="H306" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I306" t="str">
-        <v/>
       </c>
     </row>
     <row r="307">
@@ -28714,9 +26884,6 @@
       <c r="C307" t="str">
         <v>DGM(SA)</v>
       </c>
-      <c r="D307" t="str">
-        <v/>
-      </c>
       <c r="E307" t="str">
         <v>Smt. Santhi</v>
       </c>
@@ -28728,9 +26895,6 @@
       </c>
       <c r="H307" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I307" t="str">
-        <v/>
       </c>
     </row>
     <row r="308">
@@ -28743,9 +26907,6 @@
       <c r="C308" t="str">
         <v>AGM(SD)</v>
       </c>
-      <c r="D308" t="str">
-        <v/>
-      </c>
       <c r="E308" t="str">
         <v>PADMA DEVI R</v>
       </c>
@@ -28757,9 +26918,6 @@
       </c>
       <c r="H308" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I308" t="str">
-        <v/>
       </c>
     </row>
     <row r="309">
@@ -28772,9 +26930,6 @@
       <c r="C309" t="str">
         <v>AGM(SA)</v>
       </c>
-      <c r="D309" t="str">
-        <v/>
-      </c>
       <c r="E309" t="str">
         <v>Smt.Vairamathy K</v>
       </c>
@@ -28786,9 +26941,6 @@
       </c>
       <c r="H309" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I309" t="str">
-        <v/>
       </c>
     </row>
     <row r="310">
@@ -28801,9 +26953,6 @@
       <c r="C310" t="str">
         <v>SDE SA</v>
       </c>
-      <c r="D310" t="str">
-        <v/>
-      </c>
       <c r="E310" t="str">
         <v>Smt. Anuradha P</v>
       </c>
@@ -28815,9 +26964,6 @@
       </c>
       <c r="H310" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I310" t="str">
-        <v/>
       </c>
     </row>
     <row r="311">
@@ -28830,9 +26976,6 @@
       <c r="C311" t="str">
         <v>SDE SA</v>
       </c>
-      <c r="D311" t="str">
-        <v/>
-      </c>
       <c r="E311" t="str">
         <v>Shri Venkata Suresh P</v>
       </c>
@@ -28844,9 +26987,6 @@
       </c>
       <c r="H311" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I311" t="str">
-        <v/>
       </c>
     </row>
     <row r="312">
@@ -28859,9 +26999,6 @@
       <c r="C312" t="str">
         <v>JTO(SD)</v>
       </c>
-      <c r="D312" t="str">
-        <v/>
-      </c>
       <c r="E312" t="str">
         <v>Smt .Mercy Rani T</v>
       </c>
@@ -28873,9 +27010,6 @@
       </c>
       <c r="H312" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I312" t="str">
-        <v/>
       </c>
     </row>
     <row r="313">
@@ -28888,9 +27022,6 @@
       <c r="C313" t="str">
         <v>JTO(SD)</v>
       </c>
-      <c r="D313" t="str">
-        <v/>
-      </c>
       <c r="E313" t="str">
         <v>JOSEPH STALIN G</v>
       </c>
@@ -28902,9 +27033,6 @@
       </c>
       <c r="H313" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I313" t="str">
-        <v/>
       </c>
     </row>
     <row r="314">
@@ -28917,9 +27045,6 @@
       <c r="C314" t="str">
         <v>JTO DOP</v>
       </c>
-      <c r="D314" t="str">
-        <v/>
-      </c>
       <c r="E314" t="str">
         <v>GEETHARAMANI.S</v>
       </c>
@@ -28931,9 +27056,6 @@
       </c>
       <c r="H314" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I314" t="str">
-        <v/>
       </c>
     </row>
     <row r="315">
@@ -28946,9 +27068,6 @@
       <c r="C315" t="str">
         <v>CGM</v>
       </c>
-      <c r="D315" t="str">
-        <v/>
-      </c>
       <c r="E315" t="str">
         <v>Shri G Ratna Kumar</v>
       </c>
@@ -28960,9 +27079,6 @@
       </c>
       <c r="H315" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I315" t="str">
-        <v/>
       </c>
     </row>
     <row r="316">
@@ -28975,9 +27091,6 @@
       <c r="C316" t="str">
         <v>GM (EB Platinum)</v>
       </c>
-      <c r="D316" t="str">
-        <v/>
-      </c>
       <c r="E316" t="str">
         <v>Shri M. Bhadru</v>
       </c>
@@ -28989,9 +27102,6 @@
       </c>
       <c r="H316" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I316" t="str">
-        <v/>
       </c>
     </row>
     <row r="317">
@@ -29004,9 +27114,6 @@
       <c r="C317" t="str">
         <v>DGM (EB Platinum)</v>
       </c>
-      <c r="D317" t="str">
-        <v/>
-      </c>
       <c r="E317" t="str">
         <v>Shri Vazeeruddin Shaik</v>
       </c>
@@ -29018,9 +27125,6 @@
       </c>
       <c r="H317" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I317" t="str">
-        <v/>
       </c>
     </row>
     <row r="318">
@@ -29033,9 +27137,6 @@
       <c r="C318" t="str">
         <v>AGM (EBP Sales)</v>
       </c>
-      <c r="D318" t="str">
-        <v/>
-      </c>
       <c r="E318" t="str">
         <v>Shri Madhava Rao MV</v>
       </c>
@@ -29047,9 +27148,6 @@
       </c>
       <c r="H318" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I318" t="str">
-        <v/>
       </c>
     </row>
     <row r="319">
@@ -29062,9 +27160,6 @@
       <c r="C319" t="str">
         <v>AGM (EBP CRM)</v>
       </c>
-      <c r="D319" t="str">
-        <v/>
-      </c>
       <c r="E319" t="str">
         <v>Shri K. Venkatesham</v>
       </c>
@@ -29076,9 +27171,6 @@
       </c>
       <c r="H319" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I319" t="str">
-        <v/>
       </c>
     </row>
     <row r="320">
@@ -29091,9 +27183,6 @@
       <c r="C320" t="str">
         <v>SDE (EBP CRM)</v>
       </c>
-      <c r="D320" t="str">
-        <v/>
-      </c>
       <c r="E320" t="str">
         <v>Shri S. Sreenivasa Rao</v>
       </c>
@@ -29105,9 +27194,6 @@
       </c>
       <c r="H320" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I320" t="str">
-        <v/>
       </c>
     </row>
     <row r="321">
@@ -29120,9 +27206,6 @@
       <c r="C321" t="str">
         <v>JTO (EBP CRM)</v>
       </c>
-      <c r="D321" t="str">
-        <v/>
-      </c>
       <c r="E321" t="str">
         <v>Shri P Bala Venkta Raju</v>
       </c>
@@ -29134,9 +27217,6 @@
       </c>
       <c r="H321" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I321" t="str">
-        <v/>
       </c>
     </row>
     <row r="322">
@@ -29149,9 +27229,6 @@
       <c r="C322" t="str">
         <v>SDE (EBP CRM)</v>
       </c>
-      <c r="D322" t="str">
-        <v/>
-      </c>
       <c r="E322" t="str">
         <v>Shri Vishwanatham Bale</v>
       </c>
@@ -29163,9 +27240,6 @@
       </c>
       <c r="H322" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I322" t="str">
-        <v/>
       </c>
     </row>
     <row r="323">
@@ -29178,9 +27252,6 @@
       <c r="C323" t="str">
         <v>SDE (EBP CRM)</v>
       </c>
-      <c r="D323" t="str">
-        <v/>
-      </c>
       <c r="E323" t="str">
         <v>Shri E Chakravarthy</v>
       </c>
@@ -29192,9 +27263,6 @@
       </c>
       <c r="H323" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I323" t="str">
-        <v/>
       </c>
     </row>
     <row r="324">
@@ -29207,9 +27275,6 @@
       <c r="C324" t="str">
         <v>SDE (EBP CRM)</v>
       </c>
-      <c r="D324" t="str">
-        <v/>
-      </c>
       <c r="E324" t="str">
         <v>Smt Sumana Konney</v>
       </c>
@@ -29221,9 +27286,6 @@
       </c>
       <c r="H324" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I324" t="str">
-        <v/>
       </c>
     </row>
     <row r="325">
@@ -29236,9 +27298,6 @@
       <c r="C325" t="str">
         <v>SDE (EBP CRM)</v>
       </c>
-      <c r="D325" t="str">
-        <v/>
-      </c>
       <c r="E325" t="str">
         <v>Shri Sreenivas Rudra</v>
       </c>
@@ -29250,9 +27309,6 @@
       </c>
       <c r="H325" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I325" t="str">
-        <v/>
       </c>
     </row>
     <row r="326">
@@ -29265,9 +27321,6 @@
       <c r="C326" t="str">
         <v>Sr. GM (EB Gold &amp; LC)</v>
       </c>
-      <c r="D326" t="str">
-        <v/>
-      </c>
       <c r="E326" t="str">
         <v>Shri K. Kalyan</v>
       </c>
@@ -29279,9 +27332,6 @@
       </c>
       <c r="H326" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I326" t="str">
-        <v/>
       </c>
     </row>
     <row r="327">
@@ -29294,9 +27344,6 @@
       <c r="C327" t="str">
         <v>DGM (EB Gold &amp; LC)</v>
       </c>
-      <c r="D327" t="str">
-        <v/>
-      </c>
       <c r="E327" t="str">
         <v>Shri K. Rajendra Prasad</v>
       </c>
@@ -29308,9 +27355,6 @@
       </c>
       <c r="H327" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I327" t="str">
-        <v/>
       </c>
     </row>
     <row r="328">
@@ -29323,9 +27367,6 @@
       <c r="C328" t="str">
         <v>AGM (LC)</v>
       </c>
-      <c r="D328" t="str">
-        <v/>
-      </c>
       <c r="E328" t="str">
         <v>Shri B. Suresh</v>
       </c>
@@ -29337,9 +27378,6 @@
       </c>
       <c r="H328" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I328" t="str">
-        <v/>
       </c>
     </row>
     <row r="329">
@@ -29352,9 +27390,6 @@
       <c r="C329" t="str">
         <v>SDE LC (Fault Clearance)</v>
       </c>
-      <c r="D329" t="str">
-        <v/>
-      </c>
       <c r="E329" t="str">
         <v>Shri R. Chandulal</v>
       </c>
@@ -29366,9 +27401,6 @@
       </c>
       <c r="H329" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I329" t="str">
-        <v/>
       </c>
     </row>
     <row r="330">
@@ -29381,9 +27413,6 @@
       <c r="C330" t="str">
         <v>SDE LC (Commissioning)</v>
       </c>
-      <c r="D330" t="str">
-        <v/>
-      </c>
       <c r="E330" t="str">
         <v>Shri K. Sreekanth</v>
       </c>
@@ -29395,9 +27424,6 @@
       </c>
       <c r="H330" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I330" t="str">
-        <v/>
       </c>
     </row>
     <row r="331">
@@ -29410,9 +27436,6 @@
       <c r="C331" t="str">
         <v>SDE LC (COND Correspondence)</v>
       </c>
-      <c r="D331" t="str">
-        <v/>
-      </c>
       <c r="E331" t="str">
         <v>Shri N. Krishnaiah</v>
       </c>
@@ -29424,9 +27447,6 @@
       </c>
       <c r="H331" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I331" t="str">
-        <v/>
       </c>
     </row>
     <row r="332">
@@ -29439,9 +27459,6 @@
       <c r="C332" t="str">
         <v>CGM</v>
       </c>
-      <c r="D332" t="str">
-        <v/>
-      </c>
       <c r="E332" t="str">
         <v>Shri Alok Kumar Mishra</v>
       </c>
@@ -29453,9 +27470,6 @@
       </c>
       <c r="H332" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I332" t="str">
-        <v/>
       </c>
     </row>
     <row r="333">
@@ -29468,9 +27482,6 @@
       <c r="C333" t="str">
         <v>GM (EB)</v>
       </c>
-      <c r="D333" t="str">
-        <v/>
-      </c>
       <c r="E333" t="str">
         <v>Shri Rajnish Kumar Jaiswal</v>
       </c>
@@ -29482,9 +27493,6 @@
       </c>
       <c r="H333" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I333" t="str">
-        <v/>
       </c>
     </row>
     <row r="334">
@@ -29497,9 +27505,6 @@
       <c r="C334" t="str">
         <v>DGM EB For Feasibility/New business</v>
       </c>
-      <c r="D334" t="str">
-        <v/>
-      </c>
       <c r="E334" t="str">
         <v>Shri Sunil Jain</v>
       </c>
@@ -29511,9 +27516,6 @@
       </c>
       <c r="H334" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I334" t="str">
-        <v/>
       </c>
     </row>
     <row r="335">
@@ -29526,9 +27528,6 @@
       <c r="C335" t="str">
         <v>AGM EB For Feasibility/ New business</v>
       </c>
-      <c r="D335" t="str">
-        <v/>
-      </c>
       <c r="E335" t="str">
         <v>Shri Sanjeev Kumar</v>
       </c>
@@ -29540,9 +27539,6 @@
       </c>
       <c r="H335" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I335" t="str">
-        <v/>
       </c>
     </row>
     <row r="336">
@@ -29555,9 +27551,6 @@
       <c r="C336" t="str">
         <v>ADT EB</v>
       </c>
-      <c r="D336" t="str">
-        <v/>
-      </c>
       <c r="E336" t="str">
         <v>ANCHAL VAISH</v>
       </c>
@@ -29569,9 +27562,6 @@
       </c>
       <c r="H336" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I336" t="str">
-        <v/>
       </c>
     </row>
     <row r="337">
@@ -29584,9 +27574,6 @@
       <c r="C337" t="str">
         <v>ADT EB</v>
       </c>
-      <c r="D337" t="str">
-        <v/>
-      </c>
       <c r="E337" t="str">
         <v>INDRJEET</v>
       </c>
@@ -29598,9 +27585,6 @@
       </c>
       <c r="H337" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I337" t="str">
-        <v/>
       </c>
     </row>
     <row r="338">
@@ -29613,9 +27597,6 @@
       <c r="C338" t="str">
         <v>ADT EB</v>
       </c>
-      <c r="D338" t="str">
-        <v/>
-      </c>
       <c r="E338" t="str">
         <v>MANIK RAWAL</v>
       </c>
@@ -29627,9 +27608,6 @@
       </c>
       <c r="H338" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I338" t="str">
-        <v/>
       </c>
     </row>
     <row r="339">
@@ -29642,9 +27620,6 @@
       <c r="C339" t="str">
         <v>ADT EB</v>
       </c>
-      <c r="D339" t="str">
-        <v/>
-      </c>
       <c r="E339" t="str">
         <v>S B SINGH</v>
       </c>
@@ -29656,9 +27631,6 @@
       </c>
       <c r="H339" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I339" t="str">
-        <v/>
       </c>
     </row>
     <row r="340">
@@ -29671,9 +27643,6 @@
       <c r="C340" t="str">
         <v>JTO EB</v>
       </c>
-      <c r="D340" t="str">
-        <v/>
-      </c>
       <c r="E340" t="str">
         <v>RANDHEER SINGH</v>
       </c>
@@ -29685,9 +27654,6 @@
       </c>
       <c r="H340" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I340" t="str">
-        <v/>
       </c>
     </row>
     <row r="341">
@@ -29700,9 +27666,6 @@
       <c r="C341" t="str">
         <v>JE EB (Feasibility)</v>
       </c>
-      <c r="D341" t="str">
-        <v/>
-      </c>
       <c r="E341" t="str">
         <v>Saurabh Kumar</v>
       </c>
@@ -29714,9 +27677,6 @@
       </c>
       <c r="H341" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I341" t="str">
-        <v/>
       </c>
     </row>
     <row r="342">
@@ -29729,9 +27689,6 @@
       <c r="C342" t="str">
         <v>DGM NC</v>
       </c>
-      <c r="D342" t="str">
-        <v/>
-      </c>
       <c r="E342" t="str">
         <v>Shri Prem Chandra</v>
       </c>
@@ -29743,9 +27700,6 @@
       </c>
       <c r="H342" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I342" t="str">
-        <v/>
       </c>
     </row>
     <row r="343">
@@ -29758,9 +27712,6 @@
       <c r="C343" t="str">
         <v>AGM</v>
       </c>
-      <c r="D343" t="str">
-        <v/>
-      </c>
       <c r="E343" t="str">
         <v>Shri Virendra Ram</v>
       </c>
@@ -29772,9 +27723,6 @@
       </c>
       <c r="H343" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I343" t="str">
-        <v/>
       </c>
     </row>
     <row r="344">
@@ -29787,9 +27735,6 @@
       <c r="C344" t="str">
         <v>AD</v>
       </c>
-      <c r="D344" t="str">
-        <v/>
-      </c>
       <c r="E344" t="str">
         <v>Shri Rajeev Kumar</v>
       </c>
@@ -29801,9 +27746,6 @@
       </c>
       <c r="H344" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I344" t="str">
-        <v/>
       </c>
     </row>
     <row r="345">
@@ -29816,9 +27758,6 @@
       <c r="C345" t="str">
         <v>AD</v>
       </c>
-      <c r="D345" t="str">
-        <v/>
-      </c>
       <c r="E345" t="str">
         <v>Shri Santosh kr Pal</v>
       </c>
@@ -29830,9 +27769,6 @@
       </c>
       <c r="H345" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I345" t="str">
-        <v/>
       </c>
     </row>
     <row r="346">
@@ -29845,9 +27781,6 @@
       <c r="C346" t="str">
         <v>AD</v>
       </c>
-      <c r="D346" t="str">
-        <v/>
-      </c>
       <c r="E346" t="str">
         <v>Shri Awadhendra</v>
       </c>
@@ -29859,9 +27792,6 @@
       </c>
       <c r="H346" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I346" t="str">
-        <v/>
       </c>
     </row>
     <row r="347">
@@ -29874,9 +27804,6 @@
       <c r="C347" t="str">
         <v>JTO</v>
       </c>
-      <c r="D347" t="str">
-        <v/>
-      </c>
       <c r="E347" t="str">
         <v>Anupma Singh</v>
       </c>
@@ -29888,9 +27815,6 @@
       </c>
       <c r="H347" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I347" t="str">
-        <v/>
       </c>
     </row>
     <row r="348">
@@ -29903,9 +27827,6 @@
       <c r="C348" t="str">
         <v>CGM</v>
       </c>
-      <c r="D348" t="str">
-        <v/>
-      </c>
       <c r="E348" t="str">
         <v>Arun Kumar Garg</v>
       </c>
@@ -29917,9 +27838,6 @@
       </c>
       <c r="H348" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I348" t="str">
-        <v/>
       </c>
     </row>
     <row r="349">
@@ -29932,9 +27850,6 @@
       <c r="C349" t="str">
         <v>PGM (EB)</v>
       </c>
-      <c r="D349" t="str">
-        <v/>
-      </c>
       <c r="E349" t="str">
         <v>Mohd Salim Beg</v>
       </c>
@@ -29946,9 +27861,6 @@
       </c>
       <c r="H349" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I349" t="str">
-        <v/>
       </c>
     </row>
     <row r="350">
@@ -29961,9 +27873,6 @@
       <c r="C350" t="str">
         <v>DGM EB(I)</v>
       </c>
-      <c r="D350" t="str">
-        <v/>
-      </c>
       <c r="E350" t="str">
         <v>Rakesh Bisht</v>
       </c>
@@ -29975,9 +27884,6 @@
       </c>
       <c r="H350" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I350" t="str">
-        <v/>
       </c>
     </row>
     <row r="351">
@@ -29990,9 +27896,6 @@
       <c r="C351" t="str">
         <v>DGM EB( II)</v>
       </c>
-      <c r="D351" t="str">
-        <v/>
-      </c>
       <c r="E351" t="str">
         <v>Sanjay Kumar Mishra</v>
       </c>
@@ -30004,9 +27907,6 @@
       </c>
       <c r="H351" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I351" t="str">
-        <v/>
       </c>
     </row>
     <row r="352">
@@ -30019,9 +27919,6 @@
       <c r="C352" t="str">
         <v>AGM (EB)</v>
       </c>
-      <c r="D352" t="str">
-        <v/>
-      </c>
       <c r="E352" t="str">
         <v>Krishna Kumar</v>
       </c>
@@ -30033,9 +27930,6 @@
       </c>
       <c r="H352" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I352" t="str">
-        <v/>
       </c>
     </row>
     <row r="353">
@@ -30048,9 +27942,6 @@
       <c r="C353" t="str">
         <v>AGM (LC)</v>
       </c>
-      <c r="D353" t="str">
-        <v/>
-      </c>
       <c r="E353" t="str">
         <v>Sanjay Kumar Joshi</v>
       </c>
@@ -30062,9 +27953,6 @@
       </c>
       <c r="H353" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I353" t="str">
-        <v/>
       </c>
     </row>
     <row r="354">
@@ -30077,9 +27965,6 @@
       <c r="C354" t="str">
         <v>ADT (EB)</v>
       </c>
-      <c r="D354" t="str">
-        <v/>
-      </c>
       <c r="E354" t="str">
         <v>Ambrish Bajpai</v>
       </c>
@@ -30091,9 +27976,6 @@
       </c>
       <c r="H354" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I354" t="str">
-        <v/>
       </c>
     </row>
     <row r="355">
@@ -30106,9 +27988,6 @@
       <c r="C355" t="str">
         <v>SDE (LC - I)</v>
       </c>
-      <c r="D355" t="str">
-        <v/>
-      </c>
       <c r="E355" t="str">
         <v>Sahab Singh</v>
       </c>
@@ -30120,9 +27999,6 @@
       </c>
       <c r="H355" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I355" t="str">
-        <v/>
       </c>
     </row>
     <row r="356">
@@ -30135,9 +28011,6 @@
       <c r="C356" t="str">
         <v>SDE (LC - II)</v>
       </c>
-      <c r="D356" t="str">
-        <v/>
-      </c>
       <c r="E356" t="str">
         <v>Deepanshu Bhardwaj</v>
       </c>
@@ -30149,9 +28022,6 @@
       </c>
       <c r="H356" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I356" t="str">
-        <v/>
       </c>
     </row>
     <row r="357">
@@ -30164,9 +28034,6 @@
       <c r="C357" t="str">
         <v>JTO (EB)</v>
       </c>
-      <c r="D357" t="str">
-        <v/>
-      </c>
       <c r="E357" t="str">
         <v>Amit Maheshwari</v>
       </c>
@@ -30178,9 +28045,6 @@
       </c>
       <c r="H357" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I357" t="str">
-        <v/>
       </c>
     </row>
     <row r="358">
@@ -30193,9 +28057,6 @@
       <c r="C358" t="str">
         <v>CGM</v>
       </c>
-      <c r="D358" t="str">
-        <v/>
-      </c>
       <c r="E358" t="str">
         <v>Kulwinder Kumar</v>
       </c>
@@ -30207,9 +28068,6 @@
       </c>
       <c r="H358" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I358" t="str">
-        <v/>
       </c>
     </row>
     <row r="359">
@@ -30222,9 +28080,6 @@
       <c r="C359" t="str">
         <v>PGM</v>
       </c>
-      <c r="D359" t="str">
-        <v/>
-      </c>
       <c r="E359" t="str">
         <v>Anshuman Gupta</v>
       </c>
@@ -30236,9 +28091,6 @@
       </c>
       <c r="H359" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I359" t="str">
-        <v/>
       </c>
     </row>
     <row r="360">
@@ -30251,9 +28103,6 @@
       <c r="C360" t="str">
         <v>DGM</v>
       </c>
-      <c r="D360" t="str">
-        <v/>
-      </c>
       <c r="E360" t="str">
         <v>Rakesh Kumar</v>
       </c>
@@ -30265,9 +28114,6 @@
       </c>
       <c r="H360" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I360" t="str">
-        <v/>
       </c>
     </row>
     <row r="361">
@@ -30280,9 +28126,6 @@
       <c r="C361" t="str">
         <v>AGM</v>
       </c>
-      <c r="D361" t="str">
-        <v/>
-      </c>
       <c r="E361" t="str">
         <v>Rajeev Ranjan Singh</v>
       </c>
@@ -30294,9 +28137,6 @@
       </c>
       <c r="H361" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I361" t="str">
-        <v/>
       </c>
     </row>
     <row r="362">
@@ -30309,9 +28149,6 @@
       <c r="C362" t="str">
         <v>JTO</v>
       </c>
-      <c r="D362" t="str">
-        <v/>
-      </c>
       <c r="E362" t="str">
         <v>Hemanti Ginsai</v>
       </c>
@@ -30323,9 +28160,6 @@
       </c>
       <c r="H362" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I362" t="str">
-        <v/>
       </c>
     </row>
     <row r="363">
@@ -30338,9 +28172,6 @@
       <c r="C363" t="str">
         <v>ADT</v>
       </c>
-      <c r="D363" t="str">
-        <v/>
-      </c>
       <c r="E363" t="str">
         <v>Peeyush Chandra Singh</v>
       </c>
@@ -30352,9 +28183,6 @@
       </c>
       <c r="H363" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I363" t="str">
-        <v/>
       </c>
     </row>
     <row r="364">
@@ -30367,9 +28195,6 @@
       <c r="C364" t="str">
         <v>JTO</v>
       </c>
-      <c r="D364" t="str">
-        <v/>
-      </c>
       <c r="E364" t="str">
         <v>Sandhya Rani Banoth</v>
       </c>
@@ -30381,9 +28206,6 @@
       </c>
       <c r="H364" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I364" t="str">
-        <v/>
       </c>
     </row>
     <row r="365">
@@ -30396,9 +28218,6 @@
       <c r="C365" t="str">
         <v>GM</v>
       </c>
-      <c r="D365" t="str">
-        <v/>
-      </c>
       <c r="E365" t="str">
         <v>Manik Ch. Pramanik</v>
       </c>
@@ -30410,9 +28229,6 @@
       </c>
       <c r="H365" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I365" t="str">
-        <v/>
       </c>
     </row>
     <row r="366">
@@ -30425,9 +28241,6 @@
       <c r="C366" t="str">
         <v>SDE</v>
       </c>
-      <c r="D366" t="str">
-        <v/>
-      </c>
       <c r="E366" t="str">
         <v>Partho Kumar Ghosh</v>
       </c>
@@ -30439,9 +28252,6 @@
       </c>
       <c r="H366" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I366" t="str">
-        <v/>
       </c>
     </row>
     <row r="367">
@@ -30454,9 +28264,6 @@
       <c r="C367" t="str">
         <v>DGM</v>
       </c>
-      <c r="D367" t="str">
-        <v/>
-      </c>
       <c r="E367" t="str">
         <v>Pradeep K Sahu</v>
       </c>
@@ -30468,9 +28275,6 @@
       </c>
       <c r="H367" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I367" t="str">
-        <v/>
       </c>
     </row>
     <row r="368">
@@ -30483,9 +28287,6 @@
       <c r="C368" t="str">
         <v>AGM</v>
       </c>
-      <c r="D368" t="str">
-        <v/>
-      </c>
       <c r="E368" t="str">
         <v>Ankush Aich</v>
       </c>
@@ -30497,9 +28298,6 @@
       </c>
       <c r="H368" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I368" t="str">
-        <v/>
       </c>
     </row>
     <row r="369">
@@ -30512,9 +28310,6 @@
       <c r="C369" t="str">
         <v>SDE</v>
       </c>
-      <c r="D369" t="str">
-        <v/>
-      </c>
       <c r="E369" t="str">
         <v>Md Aqeel Ahmad</v>
       </c>
@@ -30526,9 +28321,6 @@
       </c>
       <c r="H369" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I369" t="str">
-        <v/>
       </c>
     </row>
     <row r="370">
@@ -30541,9 +28333,6 @@
       <c r="C370" t="str">
         <v>SDE</v>
       </c>
-      <c r="D370" t="str">
-        <v/>
-      </c>
       <c r="E370" t="str">
         <v>MANIK BHATTACHARYA</v>
       </c>
@@ -30555,9 +28344,6 @@
       </c>
       <c r="H370" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I370" t="str">
-        <v/>
       </c>
     </row>
     <row r="371">
@@ -30570,9 +28356,6 @@
       <c r="C371" t="str">
         <v>JTO</v>
       </c>
-      <c r="D371" t="str">
-        <v/>
-      </c>
       <c r="E371" t="str">
         <v>Maitrayee Bagchi</v>
       </c>
@@ -30584,9 +28367,6 @@
       </c>
       <c r="H371" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I371" t="str">
-        <v/>
       </c>
     </row>
     <row r="372">
@@ -30599,9 +28379,6 @@
       <c r="C372" t="str">
         <v>CGM</v>
       </c>
-      <c r="D372" t="str">
-        <v/>
-      </c>
       <c r="E372" t="str">
         <v>M K Yadav</v>
       </c>
@@ -30613,9 +28390,6 @@
       </c>
       <c r="H372" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I372" t="str">
-        <v/>
       </c>
     </row>
     <row r="373">
@@ -30628,9 +28402,6 @@
       <c r="C373" t="str">
         <v>DE</v>
       </c>
-      <c r="D373" t="str">
-        <v/>
-      </c>
       <c r="E373" t="str">
         <v>Mr.Joney</v>
       </c>
@@ -30642,9 +28413,6 @@
       </c>
       <c r="H373" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I373" t="str">
-        <v/>
       </c>
     </row>
     <row r="374">
@@ -30657,9 +28425,6 @@
       <c r="C374" t="str">
         <v>AGM(EB)</v>
       </c>
-      <c r="D374" t="str">
-        <v/>
-      </c>
       <c r="E374" t="str">
         <v>Vinod Kulkarni Sir</v>
       </c>
@@ -30671,9 +28436,6 @@
       </c>
       <c r="H374" t="str">
         <v>Circle Office</v>
-      </c>
-      <c r="I374" t="str">
-        <v/>
       </c>
     </row>
     <row r="375">
@@ -30686,9 +28448,6 @@
       <c r="C375" t="str">
         <v>SDE</v>
       </c>
-      <c r="D375" t="str">
-        <v/>
-      </c>
       <c r="E375" t="str">
         <v>Anil Chalamsetty</v>
       </c>
@@ -30700,9 +28459,6 @@
       </c>
       <c r="H375" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I375" t="str">
-        <v/>
       </c>
     </row>
     <row r="376">
@@ -30715,9 +28471,6 @@
       <c r="C376" t="str">
         <v>JTO</v>
       </c>
-      <c r="D376" t="str">
-        <v/>
-      </c>
       <c r="E376" t="str">
         <v>Mariya Babu</v>
       </c>
@@ -30729,9 +28482,6 @@
       </c>
       <c r="H376" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I376" t="str">
-        <v/>
       </c>
     </row>
     <row r="377">
@@ -30744,9 +28494,6 @@
       <c r="C377" t="str">
         <v>JTO</v>
       </c>
-      <c r="D377" t="str">
-        <v/>
-      </c>
       <c r="E377" t="str">
         <v>Ravi kumar</v>
       </c>
@@ -30758,9 +28505,6 @@
       </c>
       <c r="H377" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I377" t="str">
-        <v/>
       </c>
     </row>
     <row r="378">
@@ -30773,9 +28517,6 @@
       <c r="C378" t="str">
         <v>JTO</v>
       </c>
-      <c r="D378" t="str">
-        <v/>
-      </c>
       <c r="E378" t="str">
         <v>Rajkumar</v>
       </c>
@@ -30787,9 +28528,6 @@
       </c>
       <c r="H378" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I378" t="str">
-        <v/>
       </c>
     </row>
     <row r="379">
@@ -30802,9 +28540,6 @@
       <c r="C379" t="str">
         <v>JTO</v>
       </c>
-      <c r="D379" t="str">
-        <v/>
-      </c>
       <c r="E379" t="str">
         <v>Sai Kiran</v>
       </c>
@@ -30816,9 +28551,6 @@
       </c>
       <c r="H379" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I379" t="str">
-        <v/>
       </c>
     </row>
     <row r="380">
@@ -30831,9 +28563,6 @@
       <c r="C380" t="str">
         <v>AGM</v>
       </c>
-      <c r="D380" t="str">
-        <v/>
-      </c>
       <c r="E380" t="str">
         <v>Ruchi Agnihothri</v>
       </c>
@@ -30845,9 +28574,6 @@
       </c>
       <c r="H380" t="str">
         <v>Guntur</v>
-      </c>
-      <c r="I380" t="str">
-        <v/>
       </c>
     </row>
     <row r="381">
@@ -30860,23 +28586,14 @@
       <c r="C381" t="str">
         <v>SDE</v>
       </c>
-      <c r="D381" t="str">
-        <v/>
-      </c>
       <c r="E381" t="str">
         <v>Krishna Rao</v>
       </c>
       <c r="F381" t="str">
         <v>9490143855</v>
       </c>
-      <c r="G381" t="str">
-        <v/>
-      </c>
       <c r="H381" t="str">
         <v>Vijayawada</v>
-      </c>
-      <c r="I381" t="str">
-        <v/>
       </c>
     </row>
     <row r="382">
@@ -30889,23 +28606,14 @@
       <c r="C382" t="str">
         <v>SDE</v>
       </c>
-      <c r="D382" t="str">
-        <v/>
-      </c>
       <c r="E382" t="str">
         <v>Vinay Kumar</v>
       </c>
       <c r="F382" t="str">
         <v>9490000479</v>
       </c>
-      <c r="G382" t="str">
-        <v/>
-      </c>
       <c r="H382" t="str">
         <v>Vijayawada</v>
-      </c>
-      <c r="I382" t="str">
-        <v/>
       </c>
     </row>
     <row r="383">
@@ -30918,23 +28626,14 @@
       <c r="C383" t="str">
         <v>JTO</v>
       </c>
-      <c r="D383" t="str">
-        <v/>
-      </c>
       <c r="E383" t="str">
         <v>Pullaiaha</v>
       </c>
       <c r="F383" t="str">
         <v>9493933989</v>
       </c>
-      <c r="G383" t="str">
-        <v/>
-      </c>
       <c r="H383" t="str">
         <v>Vijayawada</v>
-      </c>
-      <c r="I383" t="str">
-        <v/>
       </c>
     </row>
     <row r="384">
@@ -30947,23 +28646,14 @@
       <c r="C384" t="str">
         <v>SDE</v>
       </c>
-      <c r="D384" t="str">
-        <v/>
-      </c>
       <c r="E384" t="str">
         <v>Sunil</v>
       </c>
       <c r="F384" t="str">
         <v>9440000183</v>
       </c>
-      <c r="G384" t="str">
-        <v/>
-      </c>
       <c r="H384" t="str">
         <v>Vishakapatnam</v>
-      </c>
-      <c r="I384" t="str">
-        <v/>
       </c>
     </row>
     <row r="385">
@@ -30976,23 +28666,14 @@
       <c r="C385" t="str">
         <v>SDE</v>
       </c>
-      <c r="D385" t="str">
-        <v/>
-      </c>
       <c r="E385" t="str">
         <v>Ashok</v>
       </c>
       <c r="F385" t="str">
         <v>9449858646</v>
       </c>
-      <c r="G385" t="str">
-        <v/>
-      </c>
       <c r="H385" t="str">
         <v>Prakasam</v>
-      </c>
-      <c r="I385" t="str">
-        <v/>
       </c>
     </row>
     <row r="386">
@@ -31005,23 +28686,14 @@
       <c r="C386" t="str">
         <v>SDE</v>
       </c>
-      <c r="D386" t="str">
-        <v/>
-      </c>
       <c r="E386" t="str">
         <v>RajaGopal</v>
       </c>
       <c r="F386" t="str">
         <v>9490122355</v>
       </c>
-      <c r="G386" t="str">
-        <v/>
-      </c>
       <c r="H386" t="str">
         <v>Chittoor</v>
-      </c>
-      <c r="I386" t="str">
-        <v/>
       </c>
     </row>
     <row r="387">
@@ -31034,23 +28706,14 @@
       <c r="C387" t="str">
         <v>AGM</v>
       </c>
-      <c r="D387" t="str">
-        <v/>
-      </c>
       <c r="E387" t="str">
         <v>Lakshmi Narayana</v>
       </c>
       <c r="F387" t="str">
         <v>9440000760</v>
       </c>
-      <c r="G387" t="str">
-        <v/>
-      </c>
       <c r="H387" t="str">
         <v>Chittoor</v>
-      </c>
-      <c r="I387" t="str">
-        <v/>
       </c>
     </row>
     <row r="388">
@@ -31063,23 +28726,14 @@
       <c r="C388" t="str">
         <v>AGM</v>
       </c>
-      <c r="D388" t="str">
-        <v/>
-      </c>
       <c r="E388" t="str">
         <v>Kalyan</v>
       </c>
       <c r="F388" t="str">
         <v>9440000185</v>
       </c>
-      <c r="G388" t="str">
-        <v/>
-      </c>
       <c r="H388" t="str">
         <v>Chittoor</v>
-      </c>
-      <c r="I388" t="str">
-        <v/>
       </c>
     </row>
     <row r="389">
@@ -31092,23 +28746,14 @@
       <c r="C389" t="str">
         <v>JTO CRM</v>
       </c>
-      <c r="D389" t="str">
-        <v/>
-      </c>
       <c r="E389" t="str">
         <v>Swapana</v>
       </c>
       <c r="F389" t="str">
         <v>8985852995</v>
       </c>
-      <c r="G389" t="str">
-        <v/>
-      </c>
       <c r="H389" t="str">
         <v>Chittoor</v>
-      </c>
-      <c r="I389" t="str">
-        <v/>
       </c>
     </row>
     <row r="390">
@@ -31121,23 +28766,14 @@
       <c r="C390" t="str">
         <v>SDE PCM</v>
       </c>
-      <c r="D390" t="str">
-        <v/>
-      </c>
       <c r="E390" t="str">
         <v>Obula Reddy</v>
       </c>
       <c r="F390" t="str">
         <v>9490122488</v>
       </c>
-      <c r="G390" t="str">
-        <v/>
-      </c>
       <c r="H390" t="str">
         <v>Chittoor</v>
-      </c>
-      <c r="I390" t="str">
-        <v/>
       </c>
     </row>
     <row r="391">
@@ -31150,23 +28786,14 @@
       <c r="C391" t="str">
         <v>SDE</v>
       </c>
-      <c r="D391" t="str">
-        <v/>
-      </c>
       <c r="E391" t="str">
         <v>Surya Hanumanthu</v>
       </c>
       <c r="F391" t="str">
         <v>9491304522</v>
       </c>
-      <c r="G391" t="str">
-        <v/>
-      </c>
       <c r="H391" t="str">
         <v>Srikakulam</v>
-      </c>
-      <c r="I391" t="str">
-        <v/>
       </c>
     </row>
     <row r="392">
@@ -31179,23 +28806,14 @@
       <c r="C392" t="str">
         <v>SDE</v>
       </c>
-      <c r="D392" t="str">
-        <v/>
-      </c>
       <c r="E392" t="str">
         <v>Hari Prasad</v>
       </c>
       <c r="F392" t="str">
         <v>9441000421</v>
       </c>
-      <c r="G392" t="str">
-        <v/>
-      </c>
       <c r="H392" t="str">
         <v>Vijayanagaram</v>
-      </c>
-      <c r="I392" t="str">
-        <v/>
       </c>
     </row>
     <row r="393">
@@ -31208,23 +28826,14 @@
       <c r="C393" t="str">
         <v>SDE</v>
       </c>
-      <c r="D393" t="str">
-        <v/>
-      </c>
       <c r="E393" t="str">
         <v>Munisekhar</v>
       </c>
       <c r="F393" t="str">
         <v>9449002816</v>
       </c>
-      <c r="G393" t="str">
-        <v/>
-      </c>
       <c r="H393" t="str">
         <v>Nellore</v>
-      </c>
-      <c r="I393" t="str">
-        <v/>
       </c>
     </row>
     <row r="394">
@@ -31237,23 +28846,14 @@
       <c r="C394" t="str">
         <v>SDE</v>
       </c>
-      <c r="D394" t="str">
-        <v/>
-      </c>
       <c r="E394" t="str">
         <v>Karthik Gowtham</v>
       </c>
       <c r="F394" t="str">
         <v>9449025412</v>
       </c>
-      <c r="G394" t="str">
-        <v/>
-      </c>
       <c r="H394" t="str">
         <v>Nellore</v>
-      </c>
-      <c r="I394" t="str">
-        <v/>
       </c>
     </row>
     <row r="395">
@@ -31266,23 +28866,14 @@
       <c r="C395" t="str">
         <v>JTO</v>
       </c>
-      <c r="D395" t="str">
-        <v/>
-      </c>
       <c r="E395" t="str">
         <v>Ravi kumar</v>
       </c>
       <c r="F395" t="str">
         <v>9491055030</v>
       </c>
-      <c r="G395" t="str">
-        <v/>
-      </c>
       <c r="H395" t="str">
         <v>Rajamundry</v>
-      </c>
-      <c r="I395" t="str">
-        <v/>
       </c>
     </row>
     <row r="396">
@@ -31295,23 +28886,14 @@
       <c r="C396" t="str">
         <v>SDE PCM</v>
       </c>
-      <c r="D396" t="str">
-        <v/>
-      </c>
       <c r="E396" t="str">
         <v>Naveen Kumar</v>
       </c>
       <c r="F396" t="str">
         <v>9490141113</v>
       </c>
-      <c r="G396" t="str">
-        <v/>
-      </c>
       <c r="H396" t="str">
         <v>Rajamundry</v>
-      </c>
-      <c r="I396" t="str">
-        <v/>
       </c>
     </row>
     <row r="397">
@@ -31324,23 +28906,14 @@
       <c r="C397" t="str">
         <v>JTO</v>
       </c>
-      <c r="D397" t="str">
-        <v/>
-      </c>
       <c r="E397" t="str">
         <v>Yugandhar</v>
       </c>
       <c r="F397" t="str">
         <v>9491371632</v>
       </c>
-      <c r="G397" t="str">
-        <v/>
-      </c>
       <c r="H397" t="str">
         <v>Eluru</v>
-      </c>
-      <c r="I397" t="str">
-        <v/>
       </c>
     </row>
     <row r="398">
@@ -31353,23 +28926,14 @@
       <c r="C398" t="str">
         <v>SDE PCM</v>
       </c>
-      <c r="D398" t="str">
-        <v/>
-      </c>
       <c r="E398" t="str">
         <v>Aashirvadham</v>
       </c>
       <c r="F398" t="str">
         <v>9490112008</v>
       </c>
-      <c r="G398" t="str">
-        <v/>
-      </c>
       <c r="H398" t="str">
         <v>Eluru</v>
-      </c>
-      <c r="I398" t="str">
-        <v/>
       </c>
     </row>
     <row r="399">
@@ -31382,23 +28946,14 @@
       <c r="C399" t="str">
         <v>SDE EB</v>
       </c>
-      <c r="D399" t="str">
-        <v/>
-      </c>
       <c r="E399" t="str">
         <v>Srinivasa Reddy</v>
       </c>
       <c r="F399" t="str">
         <v>9420685969</v>
       </c>
-      <c r="G399" t="str">
-        <v/>
-      </c>
       <c r="H399" t="str">
         <v>Ananthapur</v>
-      </c>
-      <c r="I399" t="str">
-        <v/>
       </c>
     </row>
     <row r="400">
@@ -31411,23 +28966,14 @@
       <c r="C400" t="str">
         <v>SDE PCM</v>
       </c>
-      <c r="D400" t="str">
-        <v/>
-      </c>
       <c r="E400" t="str">
         <v>Chinmaya</v>
       </c>
       <c r="F400" t="str">
         <v>9493406450</v>
       </c>
-      <c r="G400" t="str">
-        <v/>
-      </c>
       <c r="H400" t="str">
         <v>Ananthapur</v>
-      </c>
-      <c r="I400" t="str">
-        <v/>
       </c>
     </row>
     <row r="401">
@@ -31440,23 +28986,11 @@
       <c r="C401" t="str">
         <v>JTO TX</v>
       </c>
-      <c r="D401" t="str">
-        <v/>
-      </c>
-      <c r="E401" t="str">
-        <v/>
-      </c>
       <c r="F401" t="str">
         <v>9494137877</v>
       </c>
-      <c r="G401" t="str">
-        <v/>
-      </c>
       <c r="H401" t="str">
         <v>Ananthapur</v>
-      </c>
-      <c r="I401" t="str">
-        <v/>
       </c>
     </row>
     <row r="402">
@@ -31469,23 +29003,14 @@
       <c r="C402" t="str">
         <v>JTO EB</v>
       </c>
-      <c r="D402" t="str">
-        <v/>
-      </c>
       <c r="E402" t="str">
         <v>Ranjith</v>
       </c>
       <c r="F402" t="str">
         <v>9441249545</v>
       </c>
-      <c r="G402" t="str">
-        <v/>
-      </c>
       <c r="H402" t="str">
         <v>Ananthapur</v>
-      </c>
-      <c r="I402" t="str">
-        <v/>
       </c>
     </row>
     <row r="403">
@@ -31498,23 +29023,14 @@
       <c r="C403" t="str">
         <v>AGM EB/ PV/FTTH</v>
       </c>
-      <c r="D403" t="str">
-        <v/>
-      </c>
       <c r="E403" t="str">
         <v>Ram Prakash</v>
       </c>
       <c r="F403" t="str">
         <v>9486105950</v>
       </c>
-      <c r="G403" t="str">
-        <v/>
-      </c>
       <c r="H403" t="str">
         <v>Kadapa</v>
-      </c>
-      <c r="I403" t="str">
-        <v/>
       </c>
     </row>
     <row r="404">
@@ -31527,23 +29043,14 @@
       <c r="C404" t="str">
         <v>SD EB</v>
       </c>
-      <c r="D404" t="str">
-        <v/>
-      </c>
       <c r="E404" t="str">
         <v>Vijay Kuamr</v>
       </c>
       <c r="F404" t="str">
         <v>9490000195</v>
       </c>
-      <c r="G404" t="str">
-        <v/>
-      </c>
       <c r="H404" t="str">
         <v>Kurnool</v>
-      </c>
-      <c r="I404" t="str">
-        <v/>
       </c>
     </row>
     <row r="405">
@@ -31556,9 +29063,6 @@
       <c r="C405" t="str">
         <v>—</v>
       </c>
-      <c r="D405" t="str">
-        <v/>
-      </c>
       <c r="E405" t="str">
         <v>9486101194</v>
       </c>
@@ -31570,9 +29074,6 @@
       </c>
       <c r="H405" t="str">
         <v>—</v>
-      </c>
-      <c r="I405" t="str">
-        <v/>
       </c>
     </row>
     <row r="406">
@@ -40669,9 +38170,6 @@
       <c r="F5" t="str">
         <v>0863-2370922</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -40692,9 +38190,6 @@
       <c r="F6" t="str">
         <v>9894660141</v>
       </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -40715,9 +38210,6 @@
       <c r="F7" t="str">
         <v>7780506556</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -40738,9 +38230,6 @@
       <c r="F8" t="str">
         <v>9444269837</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -40853,9 +38342,6 @@
       <c r="F13" t="str">
         <v>8328301237</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -40876,9 +38362,6 @@
       <c r="F14" t="str">
         <v>9908696681</v>
       </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -40922,9 +38405,6 @@
       <c r="F16" t="str">
         <v>9493151563</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -41005,14 +38485,8 @@
       <c r="C20" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
       <c r="E20" t="str">
         <v>MD APTS</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
       </c>
       <c r="G20" t="str">
         <v>md_apts@ap.gov.in</v>
@@ -41034,9 +38508,6 @@
       <c r="E21" t="str">
         <v>Director ITE&amp;C</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
       <c r="G21" t="str">
         <v>dv.chalam@ap.gov.in</v>
       </c>
@@ -41100,14 +38571,8 @@
       <c r="D24" t="str">
         <v>Ajay</v>
       </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
       <c r="F24" t="str">
         <v>9886799510</v>
-      </c>
-      <c r="G24" t="str">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -41123,9 +38588,6 @@
       <c r="D25" t="str">
         <v>Ramesh</v>
       </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
       <c r="F25" t="str">
         <v>7095599100</v>
       </c>
@@ -41146,9 +38608,6 @@
       <c r="D26" t="str">
         <v>Teja</v>
       </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
       <c r="F26" t="str">
         <v>7095599078</v>
       </c>
@@ -41169,9 +38628,6 @@
       <c r="D27" t="str">
         <v>Yarshad</v>
       </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
       <c r="F27" t="str">
         <v>8008344994</v>
       </c>
@@ -41192,9 +38648,6 @@
       <c r="D28" t="str">
         <v>saritha</v>
       </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
       <c r="F28" t="str">
         <v>7095599848</v>
       </c>
@@ -41244,9 +38697,6 @@
       <c r="F30" t="str">
         <v>7095599822</v>
       </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -41290,9 +38740,6 @@
       <c r="F32" t="str">
         <v>9515000616</v>
       </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -41310,12 +38757,6 @@
       <c r="E33" t="str">
         <v>Registrar IT staff</v>
       </c>
-      <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -41336,9 +38777,6 @@
       <c r="F34" t="str">
         <v>9494777799 7901625189 7569458775</v>
       </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -41358,9 +38796,6 @@
       </c>
       <c r="F35" t="str">
         <v>9985557738</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
       </c>
     </row>
     <row r="36">

--- a/Tables (1).xlsx
+++ b/Tables (1).xlsx
@@ -38057,7 +38057,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:O36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38067,19 +38067,43 @@
         <v>Company name</v>
       </c>
       <c r="C1" t="str">
-        <v>Location</v>
+        <v>Circle</v>
       </c>
       <c r="D1" t="str">
+        <v>BA Name</v>
+      </c>
+      <c r="E1" t="str">
         <v>Contact name</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Designation</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Contact no</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>mail id</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Service Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Installation Address</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Bandwidth / Plan</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Circuit ID</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Billing Account No</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Date of Commission</v>
+      </c>
+      <c r="O1" t="str">
+        <v>WAN IP Address</v>
       </c>
     </row>
     <row r="2">
@@ -38092,16 +38116,16 @@
       <c r="C2" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Ramu Nalluri</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>IT Manager</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>9618599503</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>it.manager@vitap.ac.in</v>
       </c>
     </row>
@@ -38115,16 +38139,16 @@
       <c r="C3" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Nanda Kumar</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Deputy Director</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>9840909833</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>deputydir.cts@vitap.ac.in</v>
       </c>
     </row>
@@ -38138,16 +38162,16 @@
       <c r="C4" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>Suresh</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Purchase Manager</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>9533343625</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>purchase@vitap.ac.in</v>
       </c>
     </row>
@@ -38161,13 +38185,13 @@
       <c r="C5" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Bhanu</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Receptionist</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>0863-2370922</v>
       </c>
     </row>
@@ -38181,13 +38205,13 @@
       <c r="C6" t="str">
         <v>VIT Vellore</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>Yuvaraj</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>Director PA</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>9894660141</v>
       </c>
     </row>
@@ -38201,13 +38225,13 @@
       <c r="C7" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>Venkata krishna</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Purchase sims</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>7780506556</v>
       </c>
     </row>
@@ -38221,13 +38245,13 @@
       <c r="C8" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>Suresh</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>Asst Manager</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>9444269837</v>
       </c>
     </row>
@@ -38241,16 +38265,16 @@
       <c r="C9" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D9" t="str">
+      <c r="E9" t="str">
         <v>Poornima L</v>
       </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
         <v>Manager  IT-Bills</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>9600160077</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>poornima.l@srmap.edu.in</v>
       </c>
     </row>
@@ -38264,16 +38288,16 @@
       <c r="C10" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D10" t="str">
+      <c r="E10" t="str">
         <v>Suhasini</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>Asst Director</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>7397265412</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>suhasini.b@srmap.edu.in</v>
       </c>
     </row>
@@ -38287,16 +38311,16 @@
       <c r="C11" t="str">
         <v>Inavolu-Amaravathi</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>Subrmaniyam</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>IT Manager</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>9884492740</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>datacenter@srmap.edu.in</v>
       </c>
     </row>
@@ -38310,16 +38334,16 @@
       <c r="C12" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D12" t="str">
+      <c r="E12" t="str">
         <v>Sivaram</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>IT Manager</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>9550987700</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>tm-apscan@ap.gov.in</v>
       </c>
     </row>
@@ -38333,13 +38357,13 @@
       <c r="C13" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>Naqueeb</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>IT staff</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>8328301237</v>
       </c>
     </row>
@@ -38353,13 +38377,13 @@
       <c r="C14" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>Rajesh</v>
       </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
         <v>IT staff</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>9908696681</v>
       </c>
     </row>
@@ -38373,16 +38397,16 @@
       <c r="C15" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D15" t="str">
+      <c r="E15" t="str">
         <v>Sreenivas Chirla</v>
       </c>
-      <c r="E15" t="str">
+      <c r="F15" t="str">
         <v>IT Director PA</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>8008040480</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>consultant-infra-itc@ap.gov.in</v>
       </c>
     </row>
@@ -38396,13 +38420,13 @@
       <c r="C16" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>Manikanta</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>IT staff</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>9493151563</v>
       </c>
     </row>
@@ -38416,16 +38440,16 @@
       <c r="C17" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="D17" t="str">
+      <c r="E17" t="str">
         <v>Sridhar Reddy</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>Technical Consultant</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>9963029412</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Sreedharreddy.A@gov.in</v>
       </c>
     </row>
@@ -38439,16 +38463,16 @@
       <c r="C18" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="D18" t="str">
+      <c r="E18" t="str">
         <v>Sailaja M</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
         <v>IT Manager</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>8474756522</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>msailaja-ap@nic.in</v>
       </c>
     </row>
@@ -38462,16 +38486,16 @@
       <c r="C19" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="D19" t="str">
+      <c r="E19" t="str">
         <v>Chalapathi Dasari</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
         <v>Clerk</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>9030110410</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>deo-iip-apts@ap.gov.in</v>
       </c>
     </row>
@@ -38485,10 +38509,10 @@
       <c r="C20" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>MD APTS</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>md_apts@ap.gov.in</v>
       </c>
     </row>
@@ -38502,13 +38526,13 @@
       <c r="C21" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D21" t="str">
+      <c r="E21" t="str">
         <v>D Venkatachalam</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
         <v>Director ITE&amp;C</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>dv.chalam@ap.gov.in</v>
       </c>
     </row>
@@ -38522,16 +38546,16 @@
       <c r="C22" t="str">
         <v>AP Secretariat</v>
       </c>
-      <c r="D22" t="str">
+      <c r="E22" t="str">
         <v>K Dhavuryan Naik</v>
       </c>
-      <c r="E22" t="str">
+      <c r="F22" t="str">
         <v>Director ITE&amp;C</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>9963029418</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>dir_comm_itc@ap.gov.in</v>
       </c>
     </row>
@@ -38545,16 +38569,16 @@
       <c r="C23" t="str">
         <v>APTS-Vijayawada</v>
       </c>
-      <c r="D23" t="str">
+      <c r="E23" t="str">
         <v>G.Vinod Kumar</v>
       </c>
-      <c r="E23" t="str">
+      <c r="F23" t="str">
         <v>Clerk</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>9491113416</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>vinodkumar.g16@nic.in</v>
       </c>
     </row>
@@ -38568,10 +38592,10 @@
       <c r="C24" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D24" t="str">
+      <c r="E24" t="str">
         <v>Ajay</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>9886799510</v>
       </c>
     </row>
@@ -38585,13 +38609,13 @@
       <c r="C25" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>Ramesh</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>7095599100</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>ramesh@apcrda.org</v>
       </c>
     </row>
@@ -38605,13 +38629,13 @@
       <c r="C26" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D26" t="str">
+      <c r="E26" t="str">
         <v>Teja</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>7095599078</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>itsupport@apcrda.org</v>
       </c>
     </row>
@@ -38625,13 +38649,13 @@
       <c r="C27" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D27" t="str">
+      <c r="E27" t="str">
         <v>Yarshad</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>8008344994</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>itsupport@apcrda.org</v>
       </c>
     </row>
@@ -38645,13 +38669,13 @@
       <c r="C28" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D28" t="str">
+      <c r="E28" t="str">
         <v>saritha</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>7095599848</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>itsupport@apcrda.org</v>
       </c>
     </row>
@@ -38665,16 +38689,16 @@
       <c r="C29" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D29" t="str">
+      <c r="E29" t="str">
         <v>Lakshmi Prasanna</v>
       </c>
-      <c r="E29" t="str">
+      <c r="F29" t="str">
         <v>PM IT</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <v>7995015782</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>prasanna.m@apcrda.org</v>
       </c>
     </row>
@@ -38688,13 +38712,13 @@
       <c r="C30" t="str">
         <v>Rayapudi</v>
       </c>
-      <c r="D30" t="str">
+      <c r="E30" t="str">
         <v>Nadumpalli Srinivas</v>
       </c>
-      <c r="E30" t="str">
+      <c r="F30" t="str">
         <v>PA to Comissioner</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <v>7095599822</v>
       </c>
     </row>
@@ -38708,16 +38732,16 @@
       <c r="C31" t="str">
         <v>Nelapadu Amaravathi</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>Edukondalu</v>
       </c>
-      <c r="E31" t="str">
+      <c r="F31" t="str">
         <v>Registrar IT</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>7901625203 9848455669</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>cpc-ap@aij.gov.in</v>
       </c>
     </row>
@@ -38731,13 +38755,13 @@
       <c r="C32" t="str">
         <v>Nelapadu Amaravathi</v>
       </c>
-      <c r="D32" t="str">
+      <c r="E32" t="str">
         <v>Hussain vali</v>
       </c>
-      <c r="E32" t="str">
+      <c r="F32" t="str">
         <v>Registrar IT staff</v>
       </c>
-      <c r="F32" t="str">
+      <c r="G32" t="str">
         <v>9515000616</v>
       </c>
     </row>
@@ -38751,10 +38775,10 @@
       <c r="C33" t="str">
         <v>Nelapadu Amaravathi</v>
       </c>
-      <c r="D33" t="str">
+      <c r="E33" t="str">
         <v>Mobeen</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
         <v>Registrar IT staff</v>
       </c>
     </row>
@@ -38768,13 +38792,13 @@
       <c r="C34" t="str">
         <v>Nelapadu Amaravathi</v>
       </c>
-      <c r="D34" t="str">
+      <c r="E34" t="str">
         <v>Venkata Ramana</v>
       </c>
-      <c r="E34" t="str">
+      <c r="F34" t="str">
         <v>ASST registarar</v>
       </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <v>9494777799 7901625189 7569458775</v>
       </c>
     </row>
@@ -38788,13 +38812,13 @@
       <c r="C35" t="str">
         <v>Nelapadu Amaravathi</v>
       </c>
-      <c r="D35" t="str">
+      <c r="E35" t="str">
         <v>Suresh</v>
       </c>
-      <c r="E35" t="str">
+      <c r="F35" t="str">
         <v>JL section -LL related</v>
       </c>
-      <c r="F35" t="str">
+      <c r="G35" t="str">
         <v>9985557738</v>
       </c>
     </row>
@@ -38808,22 +38832,22 @@
       <c r="C36" t="str">
         <v>opposit Secretariat</v>
       </c>
-      <c r="D36" t="str">
+      <c r="E36" t="str">
         <v>N J Rao</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
         <v>Adminstrative officer</v>
       </c>
-      <c r="F36" t="str">
+      <c r="G36" t="str">
         <v>9440621433 9849682103</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>apslsauthority@yahoo.com</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O36"/>
   </ignoredErrors>
 </worksheet>
 </file>
